--- a/ETH_Predictivo.xlsx
+++ b/ETH_Predictivo.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E397"/>
+  <dimension ref="A1:E396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6675 +449,6658 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45864</v>
+        <v>45892</v>
       </c>
       <c r="B2" t="n">
-        <v>3573.151428422555</v>
+        <v>4442.711932126239</v>
       </c>
       <c r="C2" t="n">
-        <v>3289.177566263912</v>
+        <v>4190.374122372021</v>
       </c>
       <c r="D2" t="n">
-        <v>3842.115886458094</v>
+        <v>4691.225856248357</v>
       </c>
       <c r="E2" t="n">
-        <v>3741.39599609375</v>
+        <v>4776.09033203125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45865</v>
+        <v>45893</v>
       </c>
       <c r="B3" t="n">
-        <v>3613.676573331481</v>
+        <v>4474.837740576639</v>
       </c>
       <c r="C3" t="n">
-        <v>3338.762711259032</v>
+        <v>4233.270003939004</v>
       </c>
       <c r="D3" t="n">
-        <v>3880.424897600153</v>
+        <v>4696.62902744441</v>
       </c>
       <c r="E3" t="n">
-        <v>3875.24658203125</v>
+        <v>4779.6474609375</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45866</v>
+        <v>45894</v>
       </c>
       <c r="B4" t="n">
-        <v>3637.16022712296</v>
+        <v>4479.990082830197</v>
       </c>
       <c r="C4" t="n">
-        <v>3366.482235517999</v>
+        <v>4238.253672479616</v>
       </c>
       <c r="D4" t="n">
-        <v>3920.372761781479</v>
+        <v>4737.879338267193</v>
       </c>
       <c r="E4" t="n">
-        <v>3787.42578125</v>
+        <v>4372.98779296875</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45867</v>
+        <v>45895</v>
       </c>
       <c r="B5" t="n">
-        <v>3654.33188707031</v>
+        <v>4478.76645747502</v>
       </c>
       <c r="C5" t="n">
-        <v>3378.148285734817</v>
+        <v>4227.856453132818</v>
       </c>
       <c r="D5" t="n">
-        <v>3916.977557280485</v>
+        <v>4724.952534854604</v>
       </c>
       <c r="E5" t="n">
-        <v>3793.454833984375</v>
+        <v>4600.4267578125</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45868</v>
+        <v>45896</v>
       </c>
       <c r="B6" t="n">
-        <v>3700.129874633417</v>
+        <v>4497.502951398516</v>
       </c>
       <c r="C6" t="n">
-        <v>3430.984471398839</v>
+        <v>4271.887746544485</v>
       </c>
       <c r="D6" t="n">
-        <v>3962.825824023386</v>
+        <v>4734.771253592002</v>
       </c>
       <c r="E6" t="n">
-        <v>3808.20166015625</v>
+        <v>4503.39306640625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45869</v>
+        <v>45897</v>
       </c>
       <c r="B7" t="n">
-        <v>3688.392686361002</v>
+        <v>4462.202788280691</v>
       </c>
       <c r="C7" t="n">
-        <v>3418.533260741985</v>
+        <v>4246.355476254023</v>
       </c>
       <c r="D7" t="n">
-        <v>3960.332703473319</v>
+        <v>4699.475922562247</v>
       </c>
       <c r="E7" t="n">
-        <v>3696.707763671875</v>
+        <v>4507.177734375</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45870</v>
+        <v>45898</v>
       </c>
       <c r="B8" t="n">
-        <v>3727.965603824858</v>
+        <v>4463.241546744249</v>
       </c>
       <c r="C8" t="n">
-        <v>3424.436004121146</v>
+        <v>4217.643869669215</v>
       </c>
       <c r="D8" t="n">
-        <v>3978.694414886621</v>
+        <v>4696.525556372245</v>
       </c>
       <c r="E8" t="n">
-        <v>3488.365966796875</v>
+        <v>4360.15283203125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45871</v>
+        <v>45899</v>
       </c>
       <c r="B9" t="n">
-        <v>3772.854826853399</v>
+        <v>4464.100726520388</v>
       </c>
       <c r="C9" t="n">
-        <v>3529.165582479931</v>
+        <v>4235.116946928315</v>
       </c>
       <c r="D9" t="n">
-        <v>4046.727597238101</v>
+        <v>4690.26349516451</v>
       </c>
       <c r="E9" t="n">
-        <v>3392.7412109375</v>
+        <v>4374.1533203125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45872</v>
+        <v>45900</v>
       </c>
       <c r="B10" t="n">
-        <v>3834.663809293392</v>
+        <v>4484.281266677866</v>
       </c>
       <c r="C10" t="n">
-        <v>3564.692751690274</v>
+        <v>4236.251944944831</v>
       </c>
       <c r="D10" t="n">
-        <v>4097.826428861929</v>
+        <v>4711.082558834568</v>
       </c>
       <c r="E10" t="n">
-        <v>3497.379150390625</v>
+        <v>4390.01904296875</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45873</v>
+        <v>45901</v>
       </c>
       <c r="B11" t="n">
-        <v>3878.599438741495</v>
+        <v>4478.333923928467</v>
       </c>
       <c r="C11" t="n">
-        <v>3636.531294732861</v>
+        <v>4233.21378018016</v>
       </c>
       <c r="D11" t="n">
-        <v>4138.118283425062</v>
+        <v>4720.038722910165</v>
       </c>
       <c r="E11" t="n">
-        <v>3718.986083984375</v>
+        <v>4314.47021484375</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45874</v>
+        <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>3914.930156402816</v>
+        <v>4467.05071205657</v>
       </c>
       <c r="C12" t="n">
-        <v>3642.437846479725</v>
+        <v>4230.845192741007</v>
       </c>
       <c r="D12" t="n">
-        <v>4192.162589806706</v>
+        <v>4703.102696106655</v>
       </c>
       <c r="E12" t="n">
-        <v>3611.8994140625</v>
+        <v>4325.36572265625</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45875</v>
+        <v>45903</v>
       </c>
       <c r="B13" t="n">
-        <v>3978.149513907116</v>
+        <v>4476.925711813452</v>
       </c>
       <c r="C13" t="n">
-        <v>3698.134119747046</v>
+        <v>4230.265726707149</v>
       </c>
       <c r="D13" t="n">
-        <v>4245.871754030037</v>
+        <v>4713.213600754629</v>
       </c>
       <c r="E13" t="n">
-        <v>3683.920654296875</v>
+        <v>4450.38916015625</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45876</v>
+        <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>3981.678782148251</v>
+        <v>4434.07992878184</v>
       </c>
       <c r="C14" t="n">
-        <v>3729.871776752229</v>
+        <v>4197.258453147309</v>
       </c>
       <c r="D14" t="n">
-        <v>4234.966104767697</v>
+        <v>4670.490396113531</v>
       </c>
       <c r="E14" t="n">
-        <v>3914.325927734375</v>
+        <v>4298.744140625</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45877</v>
+        <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>4033.984277216403</v>
+        <v>4428.964056714204</v>
       </c>
       <c r="C15" t="n">
-        <v>3767.324603748407</v>
+        <v>4176.511824059001</v>
       </c>
       <c r="D15" t="n">
-        <v>4282.196808930154</v>
+        <v>4664.517007498246</v>
       </c>
       <c r="E15" t="n">
-        <v>4009.848876953125</v>
+        <v>4306.98876953125</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45878</v>
+        <v>45906</v>
       </c>
       <c r="B16" t="n">
-        <v>4088.741377748672</v>
+        <v>4425.090886201127</v>
       </c>
       <c r="C16" t="n">
-        <v>3816.320363189216</v>
+        <v>4181.479644610514</v>
       </c>
       <c r="D16" t="n">
-        <v>4332.30164272107</v>
+        <v>4659.120225850346</v>
       </c>
       <c r="E16" t="n">
-        <v>4263.59912109375</v>
+        <v>4274.2421875</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45879</v>
+        <v>45907</v>
       </c>
       <c r="B17" t="n">
-        <v>4157.279641537864</v>
+        <v>4441.948985650211</v>
       </c>
       <c r="C17" t="n">
-        <v>3881.627340140705</v>
+        <v>4194.823246298009</v>
       </c>
       <c r="D17" t="n">
-        <v>4402.439354981317</v>
+        <v>4686.452288526772</v>
       </c>
       <c r="E17" t="n">
-        <v>4254.2177734375</v>
+        <v>4305.34765625</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45880</v>
+        <v>45908</v>
       </c>
       <c r="B18" t="n">
-        <v>4204.596418922786</v>
+        <v>4434.034545387042</v>
       </c>
       <c r="C18" t="n">
-        <v>3930.453354933989</v>
+        <v>4197.532404836779</v>
       </c>
       <c r="D18" t="n">
-        <v>4462.330941780254</v>
+        <v>4686.274896219823</v>
       </c>
       <c r="E18" t="n">
-        <v>4226.966796875</v>
+        <v>4308.072265625</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45881</v>
+        <v>45909</v>
       </c>
       <c r="B19" t="n">
-        <v>4240.820848448449</v>
+        <v>4422.045530095254</v>
       </c>
       <c r="C19" t="n">
-        <v>3977.012703191761</v>
+        <v>4172.423118449128</v>
       </c>
       <c r="D19" t="n">
-        <v>4517.267956447123</v>
+        <v>4663.623620214391</v>
       </c>
       <c r="E19" t="n">
-        <v>4590.9248046875</v>
+        <v>4309.04150390625</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45882</v>
+        <v>45910</v>
       </c>
       <c r="B20" t="n">
-        <v>4300.381561106329</v>
+        <v>4432.346355637341</v>
       </c>
       <c r="C20" t="n">
-        <v>4047.154869161162</v>
+        <v>4208.482179189571</v>
       </c>
       <c r="D20" t="n">
-        <v>4570.884308407388</v>
+        <v>4661.259188472473</v>
       </c>
       <c r="E20" t="n">
-        <v>4756.27587890625</v>
+        <v>4349.14599609375</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45883</v>
+        <v>45911</v>
       </c>
       <c r="B21" t="n">
-        <v>4296.711582664606</v>
+        <v>4390.89764004</v>
       </c>
       <c r="C21" t="n">
-        <v>4030.218116125282</v>
+        <v>4166.420089027612</v>
       </c>
       <c r="D21" t="n">
-        <v>4566.837510777228</v>
+        <v>4636.246552923195</v>
       </c>
       <c r="E21" t="n">
-        <v>4548.16650390625</v>
+        <v>4461.2333984375</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45884</v>
+        <v>45912</v>
       </c>
       <c r="B22" t="n">
-        <v>4338.36602254841</v>
+        <v>4387.964727820341</v>
       </c>
       <c r="C22" t="n">
-        <v>4076.550128946969</v>
+        <v>4151.992436417774</v>
       </c>
       <c r="D22" t="n">
-        <v>4598.924504490308</v>
+        <v>4615.24173132338</v>
       </c>
       <c r="E22" t="n">
-        <v>4439.98876953125</v>
+        <v>4715.24609375</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45885</v>
+        <v>45913</v>
       </c>
       <c r="B23" t="n">
-        <v>4379.184498216181</v>
+        <v>4386.856543591141</v>
       </c>
       <c r="C23" t="n">
-        <v>4113.516088133922</v>
+        <v>4160.137070419671</v>
       </c>
       <c r="D23" t="n">
-        <v>4652.75181950053</v>
+        <v>4619.146690396081</v>
       </c>
       <c r="E23" t="n">
-        <v>4426.18017578125</v>
+        <v>4668.1796875</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45886</v>
+        <v>45914</v>
       </c>
       <c r="B24" t="n">
-        <v>4430.732730611511</v>
+        <v>4406.846197422425</v>
       </c>
       <c r="C24" t="n">
-        <v>4148.378559178823</v>
+        <v>4166.683518748217</v>
       </c>
       <c r="D24" t="n">
-        <v>4696.970383273791</v>
+        <v>4659.515628918672</v>
       </c>
       <c r="E24" t="n">
-        <v>4473.271484375</v>
+        <v>4609.59765625</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45887</v>
+        <v>45915</v>
       </c>
       <c r="B25" t="n">
-        <v>4458.310787514255</v>
+        <v>4402.210014849406</v>
       </c>
       <c r="C25" t="n">
-        <v>4202.38585791976</v>
+        <v>4163.376066858497</v>
       </c>
       <c r="D25" t="n">
-        <v>4746.574462202278</v>
+        <v>4650.239128421375</v>
       </c>
       <c r="E25" t="n">
-        <v>4312.5048828125</v>
+        <v>4526.8203125</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45888</v>
+        <v>45916</v>
       </c>
       <c r="B26" t="n">
-        <v>4472.409990696534</v>
+        <v>4393.396914088129</v>
       </c>
       <c r="C26" t="n">
-        <v>4176.377151535944</v>
+        <v>4143.629718858361</v>
       </c>
       <c r="D26" t="n">
-        <v>4735.147250536109</v>
+        <v>4625.095147818923</v>
       </c>
       <c r="E26" t="n">
-        <v>4073.464111328125</v>
+        <v>4503.564453125</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45889</v>
+        <v>45917</v>
       </c>
       <c r="B27" t="n">
-        <v>4507.871990146975</v>
+        <v>4406.596105507188</v>
       </c>
       <c r="C27" t="n">
-        <v>4240.240738855377</v>
+        <v>4180.445525364065</v>
       </c>
       <c r="D27" t="n">
-        <v>4768.50001802452</v>
+        <v>4644.772440929437</v>
       </c>
       <c r="E27" t="n">
-        <v>4334.50048828125</v>
+        <v>4592.7333984375</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45890</v>
+        <v>45918</v>
       </c>
       <c r="B28" t="n">
-        <v>4478.583715927686</v>
+        <v>4367.577473681227</v>
       </c>
       <c r="C28" t="n">
-        <v>4197.66421710057</v>
+        <v>4133.768424040893</v>
       </c>
       <c r="D28" t="n">
-        <v>4752.788735765876</v>
+        <v>4610.05764230652</v>
       </c>
       <c r="E28" t="n">
-        <v>4223.2099609375</v>
+        <v>4589.9189453125</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45891</v>
+        <v>45919</v>
       </c>
       <c r="B29" t="n">
-        <v>4493.584052393334</v>
+        <v>4366.43810473484</v>
       </c>
       <c r="C29" t="n">
-        <v>4222.267480293714</v>
+        <v>4111.853413314519</v>
       </c>
       <c r="D29" t="n">
-        <v>4785.888876620099</v>
+        <v>4600.415502441972</v>
       </c>
       <c r="E29" t="n">
-        <v>4831.3486328125</v>
+        <v>4470.9169921875</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45892</v>
+        <v>45920</v>
       </c>
       <c r="B30" t="n">
-        <v>4507.214471422443</v>
+        <v>4366.346343070876</v>
       </c>
       <c r="C30" t="n">
-        <v>4247.594515599548</v>
+        <v>4131.218497821565</v>
       </c>
       <c r="D30" t="n">
-        <v>4762.662501032184</v>
+        <v>4606.270376607811</v>
       </c>
       <c r="E30" t="n">
-        <v>4776.09033203125</v>
+        <v>4482.265625</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45893</v>
+        <v>45921</v>
       </c>
       <c r="B31" t="n">
-        <v>4531.548369815262</v>
+        <v>4386.466635322448</v>
       </c>
       <c r="C31" t="n">
-        <v>4264.378709934942</v>
+        <v>4156.014490959693</v>
       </c>
       <c r="D31" t="n">
-        <v>4782.403802909608</v>
+        <v>4627.708535669033</v>
       </c>
       <c r="E31" t="n">
-        <v>4779.6474609375</v>
+        <v>4451.3291015625</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45894</v>
+        <v>45922</v>
       </c>
       <c r="B32" t="n">
-        <v>4532.386911327881</v>
+        <v>4381.001703052983</v>
       </c>
       <c r="C32" t="n">
-        <v>4275.223549772893</v>
+        <v>4134.290298678132</v>
       </c>
       <c r="D32" t="n">
-        <v>4796.167733233394</v>
+        <v>4629.926135257228</v>
       </c>
       <c r="E32" t="n">
-        <v>4372.98779296875</v>
+        <v>4202.87744140625</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45895</v>
+        <v>45923</v>
       </c>
       <c r="B33" t="n">
-        <v>4520.70371793758</v>
+        <v>4370.395866768887</v>
       </c>
       <c r="C33" t="n">
-        <v>4253.625951131623</v>
+        <v>4135.03672486352</v>
       </c>
       <c r="D33" t="n">
-        <v>4787.59204042852</v>
+        <v>4594.362253993517</v>
       </c>
       <c r="E33" t="n">
-        <v>4600.4267578125</v>
+        <v>4165.50390625</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45896</v>
+        <v>45924</v>
       </c>
       <c r="B34" t="n">
-        <v>4531.792238905447</v>
+        <v>4380.807451787626</v>
       </c>
       <c r="C34" t="n">
-        <v>4269.6631821377</v>
+        <v>4155.850073057239</v>
       </c>
       <c r="D34" t="n">
-        <v>4795.13331582534</v>
+        <v>4630.64284020242</v>
       </c>
       <c r="E34" t="n">
-        <v>4503.39306640625</v>
+        <v>4153.46923828125</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45897</v>
+        <v>45925</v>
       </c>
       <c r="B35" t="n">
-        <v>4479.949819291408</v>
+        <v>4338.044586045689</v>
       </c>
       <c r="C35" t="n">
-        <v>4232.561761633193</v>
+        <v>4101.466168821546</v>
       </c>
       <c r="D35" t="n">
-        <v>4761.130026120013</v>
+        <v>4572.819906245694</v>
       </c>
       <c r="E35" t="n">
-        <v>4507.177734375</v>
+        <v>3868.333984375</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45898</v>
+        <v>45926</v>
       </c>
       <c r="B36" t="n">
-        <v>4474.574603903327</v>
+        <v>4332.277902621031</v>
       </c>
       <c r="C36" t="n">
-        <v>4222.463400319176</v>
+        <v>4098.25135624578</v>
       </c>
       <c r="D36" t="n">
-        <v>4741.247540420293</v>
+        <v>4560.359193878539</v>
       </c>
       <c r="E36" t="n">
-        <v>4360.15283203125</v>
+        <v>4035.887939453125</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45899</v>
+        <v>45927</v>
       </c>
       <c r="B37" t="n">
-        <v>4470.307773573069</v>
+        <v>4326.781575669102</v>
       </c>
       <c r="C37" t="n">
-        <v>4212.560928580845</v>
+        <v>4092.347890151299</v>
       </c>
       <c r="D37" t="n">
-        <v>4740.566775440581</v>
+        <v>4544.468849420517</v>
       </c>
       <c r="E37" t="n">
-        <v>4374.1533203125</v>
+        <v>4018.658203125</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45900</v>
+        <v>45928</v>
       </c>
       <c r="B38" t="n">
-        <v>4479.456083943944</v>
+        <v>4340.854048218607</v>
       </c>
       <c r="C38" t="n">
-        <v>4211.366146507266</v>
+        <v>4106.610066842204</v>
       </c>
       <c r="D38" t="n">
-        <v>4733.529713670781</v>
+        <v>4571.610523736462</v>
       </c>
       <c r="E38" t="n">
-        <v>4390.01904296875</v>
+        <v>4141.4765625</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45901</v>
+        <v>45929</v>
       </c>
       <c r="B39" t="n">
-        <v>4467.982681063903</v>
+        <v>4328.855126237162</v>
       </c>
       <c r="C39" t="n">
-        <v>4208.458037178861</v>
+        <v>4092.134552480921</v>
       </c>
       <c r="D39" t="n">
-        <v>4728.634854804888</v>
+        <v>4579.643822838704</v>
       </c>
       <c r="E39" t="n">
-        <v>4314.47021484375</v>
+        <v>4217.341796875</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45902</v>
+        <v>45930</v>
       </c>
       <c r="B40" t="n">
-        <v>4446.948683100996</v>
+        <v>4311.403425189129</v>
       </c>
       <c r="C40" t="n">
-        <v>4178.09868392597</v>
+        <v>4065.251845137246</v>
       </c>
       <c r="D40" t="n">
-        <v>4721.467651688505</v>
+        <v>4565.329671903888</v>
       </c>
       <c r="E40" t="n">
-        <v>4325.36572265625</v>
+        <v>4145.95751953125</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45903</v>
+        <v>45931</v>
       </c>
       <c r="B41" t="n">
-        <v>4451.659423306008</v>
+        <v>4314.842290086564</v>
       </c>
       <c r="C41" t="n">
-        <v>4192.968525057435</v>
+        <v>4067.317083430655</v>
       </c>
       <c r="D41" t="n">
-        <v>4709.936157741706</v>
+        <v>4544.693904961932</v>
       </c>
       <c r="E41" t="n">
-        <v>4450.38916015625</v>
+        <v>4351.1123046875</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45904</v>
+        <v>45932</v>
       </c>
       <c r="B42" t="n">
-        <v>4396.349407172344</v>
+        <v>4265.168709670909</v>
       </c>
       <c r="C42" t="n">
-        <v>4130.899471349917</v>
+        <v>4020.950857484847</v>
       </c>
       <c r="D42" t="n">
-        <v>4660.885717606917</v>
+        <v>4495.87256110914</v>
       </c>
       <c r="E42" t="n">
-        <v>4298.744140625</v>
+        <v>4487.923828125</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45905</v>
+        <v>45933</v>
       </c>
       <c r="B43" t="n">
-        <v>4390.282087838053</v>
+        <v>4252.738962303799</v>
       </c>
       <c r="C43" t="n">
-        <v>4131.314579660297</v>
+        <v>4019.955975823093</v>
       </c>
       <c r="D43" t="n">
-        <v>4654.349772755325</v>
+        <v>4494.079894285593</v>
       </c>
       <c r="E43" t="n">
-        <v>4306.98876953125</v>
+        <v>4514.87060546875</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45906</v>
+        <v>45934</v>
       </c>
       <c r="B44" t="n">
-        <v>4387.896871219971</v>
+        <v>4241.002654232853</v>
       </c>
       <c r="C44" t="n">
-        <v>4129.153461610443</v>
+        <v>3999.330868283849</v>
       </c>
       <c r="D44" t="n">
-        <v>4633.240318067448</v>
+        <v>4461.021564537546</v>
       </c>
       <c r="E44" t="n">
-        <v>4274.2421875</v>
+        <v>4489.197265625</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45907</v>
+        <v>45935</v>
       </c>
       <c r="B45" t="n">
-        <v>4401.238181894008</v>
+        <v>4249.416740704611</v>
       </c>
       <c r="C45" t="n">
-        <v>4133.662787501769</v>
+        <v>4018.548865648037</v>
       </c>
       <c r="D45" t="n">
-        <v>4670.444120061375</v>
+        <v>4483.232204770168</v>
       </c>
       <c r="E45" t="n">
-        <v>4305.34765625</v>
+        <v>4515.4228515625</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45908</v>
+        <v>45936</v>
       </c>
       <c r="B46" t="n">
-        <v>4395.95438388281</v>
+        <v>4232.476429009528</v>
       </c>
       <c r="C46" t="n">
-        <v>4118.339318445309</v>
+        <v>3996.208778545105</v>
       </c>
       <c r="D46" t="n">
-        <v>4638.370021618797</v>
+        <v>4458.920522791936</v>
       </c>
       <c r="E46" t="n">
-        <v>4308.072265625</v>
+        <v>4687.771484375</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45909</v>
+        <v>45937</v>
       </c>
       <c r="B47" t="n">
-        <v>4382.748802561895</v>
+        <v>4210.907160528844</v>
       </c>
       <c r="C47" t="n">
-        <v>4125.052245336127</v>
+        <v>3956.802305225336</v>
       </c>
       <c r="D47" t="n">
-        <v>4622.555618919947</v>
+        <v>4451.080994858445</v>
       </c>
       <c r="E47" t="n">
-        <v>4309.04150390625</v>
+        <v>4451.15185546875</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45910</v>
+        <v>45938</v>
       </c>
       <c r="B48" t="n">
-        <v>4396.536488373582</v>
+        <v>4211.125982172019</v>
       </c>
       <c r="C48" t="n">
-        <v>4151.254956737349</v>
+        <v>3980.415549359709</v>
       </c>
       <c r="D48" t="n">
-        <v>4680.013746352784</v>
+        <v>4445.782103932085</v>
       </c>
       <c r="E48" t="n">
-        <v>4349.14599609375</v>
+        <v>4527.64794921875</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45911</v>
+        <v>45939</v>
       </c>
       <c r="B49" t="n">
-        <v>4351.140471744671</v>
+        <v>4159.166990629642</v>
       </c>
       <c r="C49" t="n">
-        <v>4067.286581478652</v>
+        <v>3925.44299690271</v>
       </c>
       <c r="D49" t="n">
-        <v>4605.968215224667</v>
+        <v>4400.620565681678</v>
       </c>
       <c r="E49" t="n">
-        <v>4461.2333984375</v>
+        <v>4369.1435546875</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45912</v>
+        <v>45940</v>
       </c>
       <c r="B50" t="n">
-        <v>4355.403296014402</v>
+        <v>4145.384717228284</v>
       </c>
       <c r="C50" t="n">
-        <v>4092.79590858039</v>
+        <v>3908.369422166068</v>
       </c>
       <c r="D50" t="n">
-        <v>4620.132261721389</v>
+        <v>4360.950153708356</v>
       </c>
       <c r="E50" t="n">
-        <v>4715.24609375</v>
+        <v>3843.0087890625</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45913</v>
+        <v>45941</v>
       </c>
       <c r="B51" t="n">
-        <v>4363.345909035691</v>
+        <v>4133.187208111743</v>
       </c>
       <c r="C51" t="n">
-        <v>4101.463696498351</v>
+        <v>3898.80548931087</v>
       </c>
       <c r="D51" t="n">
-        <v>4631.200060717539</v>
+        <v>4382.339119651811</v>
       </c>
       <c r="E51" t="n">
-        <v>4668.1796875</v>
+        <v>3750.611572265625</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45914</v>
+        <v>45942</v>
       </c>
       <c r="B52" t="n">
-        <v>4386.608410113917</v>
+        <v>4141.950442905482</v>
       </c>
       <c r="C52" t="n">
-        <v>4099.725390799799</v>
+        <v>3893.865045300829</v>
       </c>
       <c r="D52" t="n">
-        <v>4666.186743379776</v>
+        <v>4376.477554898491</v>
       </c>
       <c r="E52" t="n">
-        <v>4609.59765625</v>
+        <v>4164.427734375</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45915</v>
+        <v>45943</v>
       </c>
       <c r="B53" t="n">
-        <v>4390.460118927707</v>
+        <v>4126.051003294107</v>
       </c>
       <c r="C53" t="n">
-        <v>4120.479991863599</v>
+        <v>3887.71802734769</v>
       </c>
       <c r="D53" t="n">
-        <v>4646.552538995194</v>
+        <v>4379.699491867648</v>
       </c>
       <c r="E53" t="n">
-        <v>4526.8203125</v>
+        <v>4245.4677734375</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45916</v>
+        <v>45944</v>
       </c>
       <c r="B54" t="n">
-        <v>4385.260900329014</v>
+        <v>4106.061156568718</v>
       </c>
       <c r="C54" t="n">
-        <v>4120.844574367284</v>
+        <v>3847.955530130224</v>
       </c>
       <c r="D54" t="n">
-        <v>4658.880397399589</v>
+        <v>4331.342111203065</v>
       </c>
       <c r="E54" t="n">
-        <v>4503.564453125</v>
+        <v>4125.412109375</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45917</v>
+        <v>45945</v>
       </c>
       <c r="B55" t="n">
-        <v>4405.627098034648</v>
+        <v>4108.214590492944</v>
       </c>
       <c r="C55" t="n">
-        <v>4124.348396414438</v>
+        <v>3878.489145884293</v>
       </c>
       <c r="D55" t="n">
-        <v>4687.068865606687</v>
+        <v>4346.696822108239</v>
       </c>
       <c r="E55" t="n">
-        <v>4592.7333984375</v>
+        <v>3987.45947265625</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45918</v>
+        <v>45946</v>
       </c>
       <c r="B56" t="n">
-        <v>4365.135571551807</v>
+        <v>4058.337367950103</v>
       </c>
       <c r="C56" t="n">
-        <v>4114.220064880752</v>
+        <v>3822.515274685933</v>
       </c>
       <c r="D56" t="n">
-        <v>4624.784039225168</v>
+        <v>4292.386446687292</v>
       </c>
       <c r="E56" t="n">
-        <v>4589.9189453125</v>
+        <v>3894.75439453125</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45919</v>
+        <v>45947</v>
       </c>
       <c r="B57" t="n">
-        <v>4372.441408077187</v>
+        <v>4046.557816438417</v>
       </c>
       <c r="C57" t="n">
-        <v>4125.502804432301</v>
+        <v>3796.83966023954</v>
       </c>
       <c r="D57" t="n">
-        <v>4623.180256243437</v>
+        <v>4282.551414941916</v>
       </c>
       <c r="E57" t="n">
-        <v>4470.9169921875</v>
+        <v>3832.558837890625</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45920</v>
+        <v>45948</v>
       </c>
       <c r="B58" t="n">
-        <v>4381.441220924004</v>
+        <v>4036.046920208794</v>
       </c>
       <c r="C58" t="n">
-        <v>4108.942598993091</v>
+        <v>3813.488130134835</v>
       </c>
       <c r="D58" t="n">
-        <v>4639.845180181384</v>
+        <v>4278.86169601994</v>
       </c>
       <c r="E58" t="n">
-        <v>4482.265625</v>
+        <v>3890.34619140625</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45921</v>
+        <v>45949</v>
       </c>
       <c r="B59" t="n">
-        <v>4403.71641340534</v>
+        <v>4045.940644178134</v>
       </c>
       <c r="C59" t="n">
-        <v>4142.894055997707</v>
+        <v>3805.873859828865</v>
       </c>
       <c r="D59" t="n">
-        <v>4677.291623523573</v>
+        <v>4280.525707105366</v>
       </c>
       <c r="E59" t="n">
-        <v>4451.3291015625</v>
+        <v>3984.649658203125</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45922</v>
+        <v>45950</v>
       </c>
       <c r="B60" t="n">
-        <v>4404.543810975771</v>
+        <v>4030.38086294557</v>
       </c>
       <c r="C60" t="n">
-        <v>4148.173673395816</v>
+        <v>3780.271956583364</v>
       </c>
       <c r="D60" t="n">
-        <v>4653.928957877019</v>
+        <v>4267.510743991293</v>
       </c>
       <c r="E60" t="n">
-        <v>4202.87744140625</v>
+        <v>3980.76025390625</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45923</v>
+        <v>45951</v>
       </c>
       <c r="B61" t="n">
-        <v>4394.355588290559</v>
+        <v>4009.718807759564</v>
       </c>
       <c r="C61" t="n">
-        <v>4133.21376687192</v>
+        <v>3777.678314169018</v>
       </c>
       <c r="D61" t="n">
-        <v>4656.495748789739</v>
+        <v>4245.944908613101</v>
       </c>
       <c r="E61" t="n">
-        <v>4165.50390625</v>
+        <v>3876.76416015625</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45924</v>
+        <v>45952</v>
       </c>
       <c r="B62" t="n">
-        <v>4407.901893813386</v>
+        <v>4009.989007491424</v>
       </c>
       <c r="C62" t="n">
-        <v>4156.294451670712</v>
+        <v>3774.591840081615</v>
       </c>
       <c r="D62" t="n">
-        <v>4671.069082877366</v>
+        <v>4252.172176187672</v>
       </c>
       <c r="E62" t="n">
-        <v>4153.46923828125</v>
+        <v>3808.122314453125</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45925</v>
+        <v>45953</v>
       </c>
       <c r="B63" t="n">
-        <v>4358.949770047634</v>
+        <v>3956.84803074956</v>
       </c>
       <c r="C63" t="n">
-        <v>4088.645092289898</v>
+        <v>3724.16767282514</v>
       </c>
       <c r="D63" t="n">
-        <v>4612.146234084179</v>
+        <v>4189.400552137054</v>
       </c>
       <c r="E63" t="n">
-        <v>3868.333984375</v>
+        <v>3856.0263671875</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45926</v>
+        <v>45954</v>
       </c>
       <c r="B64" t="n">
-        <v>4356.394098668968</v>
+        <v>3940.291491875983</v>
       </c>
       <c r="C64" t="n">
-        <v>4088.96332382539</v>
+        <v>3706.681934404737</v>
       </c>
       <c r="D64" t="n">
-        <v>4630.911998853422</v>
+        <v>4186.173209440607</v>
       </c>
       <c r="E64" t="n">
-        <v>4035.887939453125</v>
+        <v>3934.5673828125</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45927</v>
+        <v>45955</v>
       </c>
       <c r="B65" t="n">
-        <v>4354.412686373222</v>
+        <v>3923.400650806369</v>
       </c>
       <c r="C65" t="n">
-        <v>4098.051343862008</v>
+        <v>3673.237951034928</v>
       </c>
       <c r="D65" t="n">
-        <v>4640.702449291392</v>
+        <v>4161.051235808378</v>
       </c>
       <c r="E65" t="n">
-        <v>4018.658203125</v>
+        <v>3953.470947265625</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45928</v>
+        <v>45956</v>
       </c>
       <c r="B66" t="n">
-        <v>4364.900117115531</v>
+        <v>3925.269821358089</v>
       </c>
       <c r="C66" t="n">
-        <v>4100.398563307454</v>
+        <v>3688.931220956945</v>
       </c>
       <c r="D66" t="n">
-        <v>4636.08416727754</v>
+        <v>4161.98884525079</v>
       </c>
       <c r="E66" t="n">
-        <v>4141.4765625</v>
+        <v>4157.9892578125</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45929</v>
+        <v>45957</v>
       </c>
       <c r="B67" t="n">
-        <v>4353.468055210694</v>
+        <v>3900.051076304512</v>
       </c>
       <c r="C67" t="n">
-        <v>4091.391434446833</v>
+        <v>3669.105397180993</v>
       </c>
       <c r="D67" t="n">
-        <v>4611.262715355739</v>
+        <v>4132.498444917492</v>
       </c>
       <c r="E67" t="n">
-        <v>4217.341796875</v>
+        <v>4120.1220703125</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>45930</v>
+        <v>45958</v>
       </c>
       <c r="B68" t="n">
-        <v>4330.894234621005</v>
+        <v>3868.160012857722</v>
       </c>
       <c r="C68" t="n">
-        <v>4082.771006904679</v>
+        <v>3634.530057449874</v>
       </c>
       <c r="D68" t="n">
-        <v>4595.957329321523</v>
+        <v>4111.719979064118</v>
       </c>
       <c r="E68" t="n">
-        <v>4145.95751953125</v>
+        <v>3982.262451171875</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>45931</v>
+        <v>45959</v>
       </c>
       <c r="B69" t="n">
-        <v>4332.273863331018</v>
+        <v>3855.750445713095</v>
       </c>
       <c r="C69" t="n">
-        <v>4079.527980385002</v>
+        <v>3613.713851007666</v>
       </c>
       <c r="D69" t="n">
-        <v>4588.621444645973</v>
+        <v>4109.518673618586</v>
       </c>
       <c r="E69" t="n">
-        <v>4351.1123046875</v>
+        <v>3903.35302734375</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>45932</v>
+        <v>45960</v>
       </c>
       <c r="B70" t="n">
-        <v>4271.707376937295</v>
+        <v>3788.652271455489</v>
       </c>
       <c r="C70" t="n">
-        <v>4009.296352012117</v>
+        <v>3553.294959007987</v>
       </c>
       <c r="D70" t="n">
-        <v>4530.708793175613</v>
+        <v>4033.026546461052</v>
       </c>
       <c r="E70" t="n">
-        <v>4487.923828125</v>
+        <v>3804.375244140625</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>45933</v>
+        <v>45961</v>
       </c>
       <c r="B71" t="n">
-        <v>4258.400604215198</v>
+        <v>3757.085949690942</v>
       </c>
       <c r="C71" t="n">
-        <v>3983.085653796661</v>
+        <v>3522.878956360273</v>
       </c>
       <c r="D71" t="n">
-        <v>4523.23313099727</v>
+        <v>4014.102525822108</v>
       </c>
       <c r="E71" t="n">
-        <v>4514.87060546875</v>
+        <v>3847.080322265625</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>45934</v>
+        <v>45962</v>
       </c>
       <c r="B72" t="n">
-        <v>4246.8097843573</v>
+        <v>3724.404962975806</v>
       </c>
       <c r="C72" t="n">
-        <v>3970.760080294423</v>
+        <v>3493.551337959878</v>
       </c>
       <c r="D72" t="n">
-        <v>4513.589100707749</v>
+        <v>3985.137583125453</v>
       </c>
       <c r="E72" t="n">
-        <v>4489.197265625</v>
+        <v>3874.18798828125</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>45935</v>
+        <v>45963</v>
       </c>
       <c r="B73" t="n">
-        <v>4249.066364962562</v>
+        <v>3710.017545741195</v>
       </c>
       <c r="C73" t="n">
-        <v>3988.693953383427</v>
+        <v>3481.814077875058</v>
       </c>
       <c r="D73" t="n">
-        <v>4517.401188938315</v>
+        <v>3943.426220381351</v>
       </c>
       <c r="E73" t="n">
-        <v>4515.4228515625</v>
+        <v>3911.063232421875</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>45936</v>
+        <v>45964</v>
       </c>
       <c r="B74" t="n">
-        <v>4230.969538871654</v>
+        <v>3668.424319770161</v>
       </c>
       <c r="C74" t="n">
-        <v>3965.181054000456</v>
+        <v>3408.441594337407</v>
       </c>
       <c r="D74" t="n">
-        <v>4476.645692091694</v>
+        <v>3902.942996424393</v>
       </c>
       <c r="E74" t="n">
-        <v>4687.771484375</v>
+        <v>3602.30810546875</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>45937</v>
+        <v>45965</v>
       </c>
       <c r="B75" t="n">
-        <v>4203.428993751759</v>
+        <v>3620.415726196758</v>
       </c>
       <c r="C75" t="n">
-        <v>3961.202277883473</v>
+        <v>3379.962307549607</v>
       </c>
       <c r="D75" t="n">
-        <v>4472.943850392355</v>
+        <v>3870.442435718327</v>
       </c>
       <c r="E75" t="n">
-        <v>4451.15185546875</v>
+        <v>3292.574462890625</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>45938</v>
+        <v>45966</v>
       </c>
       <c r="B76" t="n">
-        <v>4201.611795054714</v>
+        <v>3592.53737607568</v>
       </c>
       <c r="C76" t="n">
-        <v>3935.76359650318</v>
+        <v>3342.830497323678</v>
       </c>
       <c r="D76" t="n">
-        <v>4477.99616838707</v>
+        <v>3833.333543719616</v>
       </c>
       <c r="E76" t="n">
-        <v>4527.64794921875</v>
+        <v>3425.171142578125</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>45939</v>
+        <v>45967</v>
       </c>
       <c r="B77" t="n">
-        <v>4139.62748033522</v>
+        <v>3511.017785610485</v>
       </c>
       <c r="C77" t="n">
-        <v>3874.751011107884</v>
+        <v>3285.901153765517</v>
       </c>
       <c r="D77" t="n">
-        <v>4399.699325003171</v>
+        <v>3715.372828691251</v>
       </c>
       <c r="E77" t="n">
-        <v>4369.1435546875</v>
+        <v>3312.2578125</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>45940</v>
+        <v>45968</v>
       </c>
       <c r="B78" t="n">
-        <v>4126.627516460295</v>
+        <v>3466.472217930325</v>
       </c>
       <c r="C78" t="n">
-        <v>3854.227313458063</v>
+        <v>3216.214999716647</v>
       </c>
       <c r="D78" t="n">
-        <v>4366.825650030583</v>
+        <v>3687.397756991711</v>
       </c>
       <c r="E78" t="n">
-        <v>3843.0087890625</v>
+        <v>3435.301025390625</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>45941</v>
+        <v>45969</v>
       </c>
       <c r="B79" t="n">
-        <v>4116.951591212834</v>
+        <v>3422.634285683829</v>
       </c>
       <c r="C79" t="n">
-        <v>3859.307008444679</v>
+        <v>3174.157669897614</v>
       </c>
       <c r="D79" t="n">
-        <v>4394.242882718238</v>
+        <v>3654.781868304225</v>
       </c>
       <c r="E79" t="n">
-        <v>3750.611572265625</v>
+        <v>3400.3759765625</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>45942</v>
+        <v>45970</v>
       </c>
       <c r="B80" t="n">
-        <v>4122.555641754902</v>
+        <v>3399.266913281404</v>
       </c>
       <c r="C80" t="n">
-        <v>3830.26945058403</v>
+        <v>3123.063403125072</v>
       </c>
       <c r="D80" t="n">
-        <v>4394.459269364257</v>
+        <v>3637.987556798277</v>
       </c>
       <c r="E80" t="n">
-        <v>4164.427734375</v>
+        <v>3582.621337890625</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>45943</v>
+        <v>45971</v>
       </c>
       <c r="B81" t="n">
-        <v>4109.009494460295</v>
+        <v>3351.189581699526</v>
       </c>
       <c r="C81" t="n">
-        <v>3845.392447493273</v>
+        <v>3120.881014385359</v>
       </c>
       <c r="D81" t="n">
-        <v>4373.871078998077</v>
+        <v>3581.043170409852</v>
       </c>
       <c r="E81" t="n">
-        <v>4245.4677734375</v>
+        <v>3568.4599609375</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>45944</v>
+        <v>45972</v>
       </c>
       <c r="B82" t="n">
-        <v>4086.946448750923</v>
+        <v>3299.466092512917</v>
       </c>
       <c r="C82" t="n">
-        <v>3826.472499029123</v>
+        <v>3071.792723914178</v>
       </c>
       <c r="D82" t="n">
-        <v>4355.136317719284</v>
+        <v>3521.460728997729</v>
       </c>
       <c r="E82" t="n">
-        <v>4125.412109375</v>
+        <v>3415.2822265625</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>45945</v>
+        <v>45973</v>
       </c>
       <c r="B83" t="n">
-        <v>4091.218535147716</v>
+        <v>3270.861216801208</v>
       </c>
       <c r="C83" t="n">
-        <v>3815.417961018896</v>
+        <v>3030.286942217485</v>
       </c>
       <c r="D83" t="n">
-        <v>4353.159189857871</v>
+        <v>3515.702489944225</v>
       </c>
       <c r="E83" t="n">
-        <v>3987.45947265625</v>
+        <v>3413.09423828125</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>45946</v>
+        <v>45974</v>
       </c>
       <c r="B84" t="n">
-        <v>4035.591286502996</v>
+        <v>3191.760982698406</v>
       </c>
       <c r="C84" t="n">
-        <v>3781.784748890107</v>
+        <v>2961.29664172057</v>
       </c>
       <c r="D84" t="n">
-        <v>4285.541091836117</v>
+        <v>3440.359766251566</v>
       </c>
       <c r="E84" t="n">
-        <v>3894.75439453125</v>
+        <v>3232.757080078125</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>45947</v>
+        <v>45975</v>
       </c>
       <c r="B85" t="n">
-        <v>4028.853895700861</v>
+        <v>3152.870554166651</v>
       </c>
       <c r="C85" t="n">
-        <v>3773.547410000734</v>
+        <v>2910.609592223815</v>
       </c>
       <c r="D85" t="n">
-        <v>4294.283382958093</v>
+        <v>3393.368352482797</v>
       </c>
       <c r="E85" t="n">
-        <v>3832.558837890625</v>
+        <v>3103.78564453125</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>45948</v>
+        <v>45976</v>
       </c>
       <c r="B86" t="n">
-        <v>4024.976921115363</v>
+        <v>3117.941552160411</v>
       </c>
       <c r="C86" t="n">
-        <v>3747.017906610757</v>
+        <v>2887.851026887774</v>
       </c>
       <c r="D86" t="n">
-        <v>4297.374604150919</v>
+        <v>3361.964823693633</v>
       </c>
       <c r="E86" t="n">
-        <v>3890.34619140625</v>
+        <v>3166.63134765625</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>45949</v>
+        <v>45977</v>
       </c>
       <c r="B87" t="n">
-        <v>4035.552108423426</v>
+        <v>3106.680570797323</v>
       </c>
       <c r="C87" t="n">
-        <v>3776.338022588009</v>
+        <v>2863.654610161949</v>
       </c>
       <c r="D87" t="n">
-        <v>4301.051811699407</v>
+        <v>3344.213380657577</v>
       </c>
       <c r="E87" t="n">
-        <v>3984.649658203125</v>
+        <v>3092.847412109375</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>45950</v>
+        <v>45978</v>
       </c>
       <c r="B88" t="n">
-        <v>4025.801855900831</v>
+        <v>3073.775915823027</v>
       </c>
       <c r="C88" t="n">
-        <v>3757.681093725188</v>
+        <v>2817.378564444579</v>
       </c>
       <c r="D88" t="n">
-        <v>4266.226197536046</v>
+        <v>3305.365979090382</v>
       </c>
       <c r="E88" t="n">
-        <v>3980.76025390625</v>
+        <v>3024.538818359375</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>45951</v>
+        <v>45979</v>
       </c>
       <c r="B89" t="n">
-        <v>4006.040304517896</v>
+        <v>3040.086854099472</v>
       </c>
       <c r="C89" t="n">
-        <v>3756.179319029713</v>
+        <v>2815.293515010725</v>
       </c>
       <c r="D89" t="n">
-        <v>4254.986443079737</v>
+        <v>3269.139927130737</v>
       </c>
       <c r="E89" t="n">
-        <v>3876.76416015625</v>
+        <v>3122.97900390625</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>45952</v>
+        <v>45980</v>
       </c>
       <c r="B90" t="n">
-        <v>4010.839438067234</v>
+        <v>3032.103737034257</v>
       </c>
       <c r="C90" t="n">
-        <v>3740.503767435282</v>
+        <v>2787.39919777686</v>
       </c>
       <c r="D90" t="n">
-        <v>4276.434328138518</v>
+        <v>3284.086756957065</v>
       </c>
       <c r="E90" t="n">
-        <v>3808.122314453125</v>
+        <v>3023.07080078125</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>45953</v>
+        <v>45981</v>
       </c>
       <c r="B91" t="n">
-        <v>3953.733703601803</v>
+        <v>2975.87369356119</v>
       </c>
       <c r="C91" t="n">
-        <v>3700.724574471539</v>
+        <v>2723.125418134924</v>
       </c>
       <c r="D91" t="n">
-        <v>4216.803866305579</v>
+        <v>3218.276433585733</v>
       </c>
       <c r="E91" t="n">
-        <v>3856.0263671875</v>
+        <v>2831.777587890625</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>45954</v>
+        <v>45982</v>
       </c>
       <c r="B92" t="n">
-        <v>3943.338722799383</v>
+        <v>2961.705732261847</v>
       </c>
       <c r="C92" t="n">
-        <v>3669.456867189571</v>
+        <v>2721.326673055476</v>
       </c>
       <c r="D92" t="n">
-        <v>4213.98735741056</v>
+        <v>3207.787969586845</v>
       </c>
       <c r="E92" t="n">
-        <v>3934.5673828125</v>
+        <v>2765.69921875</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>45955</v>
+        <v>45983</v>
       </c>
       <c r="B93" t="n">
-        <v>3933.515987428063</v>
+        <v>2952.906939156769</v>
       </c>
       <c r="C93" t="n">
-        <v>3681.659292254979</v>
+        <v>2726.899428417237</v>
       </c>
       <c r="D93" t="n">
-        <v>4209.356257969703</v>
+        <v>3205.633979392172</v>
       </c>
       <c r="E93" t="n">
-        <v>3953.470947265625</v>
+        <v>2767.607421875</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>45956</v>
+        <v>45984</v>
       </c>
       <c r="B94" t="n">
-        <v>3935.817882530154</v>
+        <v>2968.701310107007</v>
       </c>
       <c r="C94" t="n">
-        <v>3672.074669083503</v>
+        <v>2739.30522957432</v>
       </c>
       <c r="D94" t="n">
-        <v>4204.999821810388</v>
+        <v>3191.468463769025</v>
       </c>
       <c r="E94" t="n">
-        <v>4157.9892578125</v>
+        <v>2801.676025390625</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>45957</v>
+        <v>45985</v>
       </c>
       <c r="B95" t="n">
-        <v>3915.500388779022</v>
+        <v>2963.267989005664</v>
       </c>
       <c r="C95" t="n">
-        <v>3653.087202180171</v>
+        <v>2730.017135381537</v>
       </c>
       <c r="D95" t="n">
-        <v>4185.25080003181</v>
+        <v>3194.990571057378</v>
       </c>
       <c r="E95" t="n">
-        <v>4120.1220703125</v>
+        <v>2952.71337890625</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>45958</v>
+        <v>45986</v>
       </c>
       <c r="B96" t="n">
-        <v>3882.985324562039</v>
+        <v>2956.942907509771</v>
       </c>
       <c r="C96" t="n">
-        <v>3633.832767215647</v>
+        <v>2711.671849248782</v>
       </c>
       <c r="D96" t="n">
-        <v>4149.062947391024</v>
+        <v>3216.542663782719</v>
       </c>
       <c r="E96" t="n">
-        <v>3982.262451171875</v>
+        <v>2957.936279296875</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>45959</v>
+        <v>45987</v>
       </c>
       <c r="B97" t="n">
-        <v>3873.025452192534</v>
+        <v>2975.691868956999</v>
       </c>
       <c r="C97" t="n">
-        <v>3604.268830482503</v>
+        <v>2736.800169325825</v>
       </c>
       <c r="D97" t="n">
-        <v>4141.109169001562</v>
+        <v>3216.390284460524</v>
       </c>
       <c r="E97" t="n">
-        <v>3903.35302734375</v>
+        <v>3027.81201171875</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>45960</v>
+        <v>45988</v>
       </c>
       <c r="B98" t="n">
-        <v>3799.405956046223</v>
+        <v>2945.049428112969</v>
       </c>
       <c r="C98" t="n">
-        <v>3535.1918560544</v>
+        <v>2707.855328773102</v>
       </c>
       <c r="D98" t="n">
-        <v>4062.042343391846</v>
+        <v>3189.963069786519</v>
       </c>
       <c r="E98" t="n">
-        <v>3804.375244140625</v>
+        <v>3014.542236328125</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>45961</v>
+        <v>45989</v>
       </c>
       <c r="B99" t="n">
-        <v>3771.057925978028</v>
+        <v>2954.837056090441</v>
       </c>
       <c r="C99" t="n">
-        <v>3488.244167231601</v>
+        <v>2705.127687172783</v>
       </c>
       <c r="D99" t="n">
-        <v>4049.111128556226</v>
+        <v>3202.656787568191</v>
       </c>
       <c r="E99" t="n">
-        <v>3847.080322265625</v>
+        <v>3032.304443359375</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>45962</v>
+        <v>45990</v>
       </c>
       <c r="B100" t="n">
-        <v>3742.215859519199</v>
+        <v>2967.911921873582</v>
       </c>
       <c r="C100" t="n">
-        <v>3485.324894813679</v>
+        <v>2734.75204340532</v>
       </c>
       <c r="D100" t="n">
-        <v>4024.157965528318</v>
+        <v>3231.746937243208</v>
       </c>
       <c r="E100" t="n">
-        <v>3874.18798828125</v>
+        <v>2991.685302734375</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>45963</v>
+        <v>45991</v>
       </c>
       <c r="B101" t="n">
-        <v>3724.85370523214</v>
+        <v>3003.097484112709</v>
       </c>
       <c r="C101" t="n">
-        <v>3461.547831748058</v>
+        <v>2780.131247382674</v>
       </c>
       <c r="D101" t="n">
-        <v>3979.445273257446</v>
+        <v>3246.688920894633</v>
       </c>
       <c r="E101" t="n">
-        <v>3911.063232421875</v>
+        <v>2992.112548828125</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>45964</v>
+        <v>45992</v>
       </c>
       <c r="B102" t="n">
-        <v>3684.687029973656</v>
+        <v>3014.23233690096</v>
       </c>
       <c r="C102" t="n">
-        <v>3414.180256108043</v>
+        <v>2764.421920884236</v>
       </c>
       <c r="D102" t="n">
-        <v>3957.846110284678</v>
+        <v>3251.050620107193</v>
       </c>
       <c r="E102" t="n">
-        <v>3602.30810546875</v>
+        <v>2800.18896484375</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>45965</v>
+        <v>45993</v>
       </c>
       <c r="B103" t="n">
-        <v>3632.623448668502</v>
+        <v>3021.381005322722</v>
       </c>
       <c r="C103" t="n">
-        <v>3365.605788848696</v>
+        <v>2791.149363459893</v>
       </c>
       <c r="D103" t="n">
-        <v>3881.252018416446</v>
+        <v>3250.115762074188</v>
       </c>
       <c r="E103" t="n">
-        <v>3292.574462890625</v>
+        <v>2997.939697265625</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>45966</v>
+        <v>45994</v>
       </c>
       <c r="B104" t="n">
-        <v>3603.914957006741</v>
+        <v>3050.31446786436</v>
       </c>
       <c r="C104" t="n">
-        <v>3318.103671507479</v>
+        <v>2814.402083456047</v>
       </c>
       <c r="D104" t="n">
-        <v>3867.298490937267</v>
+        <v>3300.920417821524</v>
       </c>
       <c r="E104" t="n">
-        <v>3425.171142578125</v>
+        <v>3191.57177734375</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>45967</v>
+        <v>45995</v>
       </c>
       <c r="B105" t="n">
-        <v>3512.846024015185</v>
+        <v>3026.454538764593</v>
       </c>
       <c r="C105" t="n">
-        <v>3226.78200692399</v>
+        <v>2798.015154997946</v>
       </c>
       <c r="D105" t="n">
-        <v>3782.94682852504</v>
+        <v>3273.774092997343</v>
       </c>
       <c r="E105" t="n">
-        <v>3312.2578125</v>
+        <v>3134.31640625</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>45968</v>
+        <v>45996</v>
       </c>
       <c r="B106" t="n">
-        <v>3468.833444187764</v>
+        <v>3039.595426383151</v>
       </c>
       <c r="C106" t="n">
-        <v>3199.64515591393</v>
+        <v>2796.974211061558</v>
       </c>
       <c r="D106" t="n">
-        <v>3724.259363711401</v>
+        <v>3271.152583644773</v>
       </c>
       <c r="E106" t="n">
-        <v>3435.301025390625</v>
+        <v>3024.432861328125</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>45969</v>
+        <v>45997</v>
       </c>
       <c r="B107" t="n">
-        <v>3426.57034235098</v>
+        <v>3052.653684449736</v>
       </c>
       <c r="C107" t="n">
-        <v>3194.879529951496</v>
+        <v>2804.915000779</v>
       </c>
       <c r="D107" t="n">
-        <v>3682.306371453018</v>
+        <v>3304.362970528829</v>
       </c>
       <c r="E107" t="n">
-        <v>3400.3759765625</v>
+        <v>3040.207763671875</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>45970</v>
+        <v>45998</v>
       </c>
       <c r="B108" t="n">
-        <v>3398.449232264496</v>
+        <v>3084.597692710601</v>
       </c>
       <c r="C108" t="n">
-        <v>3160.496340185531</v>
+        <v>2842.99157426237</v>
       </c>
       <c r="D108" t="n">
-        <v>3688.362730902224</v>
+        <v>3347.988068440847</v>
       </c>
       <c r="E108" t="n">
-        <v>3582.621337890625</v>
+        <v>3061.3017578125</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>45971</v>
+        <v>45999</v>
       </c>
       <c r="B109" t="n">
-        <v>3350.552079787961</v>
+        <v>3089.493115317724</v>
       </c>
       <c r="C109" t="n">
-        <v>3080.890883707097</v>
+        <v>2840.862935374593</v>
       </c>
       <c r="D109" t="n">
-        <v>3609.104876652854</v>
+        <v>3329.118901712685</v>
       </c>
       <c r="E109" t="n">
-        <v>3568.4599609375</v>
+        <v>3125.197998046875</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>45972</v>
+        <v>46000</v>
       </c>
       <c r="B110" t="n">
-        <v>3294.089856506574</v>
+        <v>3087.7080976388</v>
       </c>
       <c r="C110" t="n">
-        <v>3014.896506321556</v>
+        <v>2851.638957793552</v>
       </c>
       <c r="D110" t="n">
-        <v>3552.53802228835</v>
+        <v>3351.262787504847</v>
       </c>
       <c r="E110" t="n">
-        <v>3415.2822265625</v>
+        <v>3321.114990234375</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>45973</v>
+        <v>46001</v>
       </c>
       <c r="B111" t="n">
-        <v>3264.545540262037</v>
+        <v>3105.386105463818</v>
       </c>
       <c r="C111" t="n">
-        <v>3013.908593445594</v>
+        <v>2860.461703388278</v>
       </c>
       <c r="D111" t="n">
-        <v>3524.223884646001</v>
+        <v>3346.066014629182</v>
       </c>
       <c r="E111" t="n">
-        <v>3413.09423828125</v>
+        <v>3325.39013671875</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>45974</v>
+        <v>46002</v>
       </c>
       <c r="B112" t="n">
-        <v>3176.354695810617</v>
+        <v>3068.380722740199</v>
       </c>
       <c r="C112" t="n">
-        <v>2923.918593994152</v>
+        <v>2825.444193501698</v>
       </c>
       <c r="D112" t="n">
-        <v>3454.072662674703</v>
+        <v>3302.79987753583</v>
       </c>
       <c r="E112" t="n">
-        <v>3232.757080078125</v>
+        <v>3237.056884765625</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>45975</v>
+        <v>46003</v>
       </c>
       <c r="B113" t="n">
-        <v>3138.99986345811</v>
+        <v>3066.96596045195</v>
       </c>
       <c r="C113" t="n">
-        <v>2855.52574988733</v>
+        <v>2823.141542169055</v>
       </c>
       <c r="D113" t="n">
-        <v>3413.072974676828</v>
+        <v>3299.606572530452</v>
       </c>
       <c r="E113" t="n">
-        <v>3103.78564453125</v>
+        <v>3084.172607421875</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>45976</v>
+        <v>46004</v>
       </c>
       <c r="B114" t="n">
-        <v>3107.151322282804</v>
+        <v>3064.573576967301</v>
       </c>
       <c r="C114" t="n">
-        <v>2844.859786284102</v>
+        <v>2812.313702455695</v>
       </c>
       <c r="D114" t="n">
-        <v>3365.038504708378</v>
+        <v>3294.95021421955</v>
       </c>
       <c r="E114" t="n">
-        <v>3166.63134765625</v>
+        <v>3116.6953125</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>45977</v>
+        <v>46005</v>
       </c>
       <c r="B115" t="n">
-        <v>3093.08924242373</v>
+        <v>3080.708869669896</v>
       </c>
       <c r="C115" t="n">
-        <v>2834.470643734621</v>
+        <v>2819.372428432782</v>
       </c>
       <c r="D115" t="n">
-        <v>3342.984876412238</v>
+        <v>3324.534724319987</v>
       </c>
       <c r="E115" t="n">
-        <v>3092.847412109375</v>
+        <v>3060.5947265625</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>45978</v>
+        <v>46006</v>
       </c>
       <c r="B116" t="n">
-        <v>3062.695227295176</v>
+        <v>3069.981740332628</v>
       </c>
       <c r="C116" t="n">
-        <v>2802.525649440412</v>
+        <v>2813.428523393044</v>
       </c>
       <c r="D116" t="n">
-        <v>3313.499575565726</v>
+        <v>3309.816037210347</v>
       </c>
       <c r="E116" t="n">
-        <v>3024.538818359375</v>
+        <v>2964.18310546875</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>45979</v>
+        <v>46007</v>
       </c>
       <c r="B117" t="n">
-        <v>3026.895716042764</v>
+        <v>3053.297172293344</v>
       </c>
       <c r="C117" t="n">
-        <v>2753.254176355777</v>
+        <v>2828.335478729601</v>
       </c>
       <c r="D117" t="n">
-        <v>3279.47747371527</v>
+        <v>3308.361015810446</v>
       </c>
       <c r="E117" t="n">
-        <v>3122.97900390625</v>
+        <v>2964.180908203125</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>45980</v>
+        <v>46008</v>
       </c>
       <c r="B118" t="n">
-        <v>3020.81112205727</v>
+        <v>3057.313411118508</v>
       </c>
       <c r="C118" t="n">
-        <v>2752.568698249453</v>
+        <v>2809.079020649526</v>
       </c>
       <c r="D118" t="n">
-        <v>3283.085377969644</v>
+        <v>3307.043480383119</v>
       </c>
       <c r="E118" t="n">
-        <v>3023.07080078125</v>
+        <v>2831.403564453125</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>45981</v>
+        <v>46009</v>
       </c>
       <c r="B119" t="n">
-        <v>2958.44469626899</v>
+        <v>3008.362555337073</v>
       </c>
       <c r="C119" t="n">
-        <v>2707.381400927095</v>
+        <v>2762.590796242106</v>
       </c>
       <c r="D119" t="n">
-        <v>3242.08309305333</v>
+        <v>3244.431656946925</v>
       </c>
       <c r="E119" t="n">
-        <v>2831.777587890625</v>
+        <v>2827.069091796875</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>45982</v>
+        <v>46010</v>
       </c>
       <c r="B120" t="n">
-        <v>2948.787138902955</v>
+        <v>2997.147491935143</v>
       </c>
       <c r="C120" t="n">
-        <v>2688.061841023758</v>
+        <v>2750.226960283836</v>
       </c>
       <c r="D120" t="n">
-        <v>3219.547108501128</v>
+        <v>3211.906883007343</v>
       </c>
       <c r="E120" t="n">
-        <v>2765.69921875</v>
+        <v>2977.970703125</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>45983</v>
+        <v>46011</v>
       </c>
       <c r="B121" t="n">
-        <v>2945.96926677002</v>
+        <v>2987.467037486099</v>
       </c>
       <c r="C121" t="n">
-        <v>2663.118148084777</v>
+        <v>2757.247556301624</v>
       </c>
       <c r="D121" t="n">
-        <v>3220.308012951443</v>
+        <v>3211.211202701548</v>
       </c>
       <c r="E121" t="n">
-        <v>2767.607421875</v>
+        <v>2977.58251953125</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>45984</v>
+        <v>46012</v>
       </c>
       <c r="B122" t="n">
-        <v>2961.697443895271</v>
+        <v>2999.121079549026</v>
       </c>
       <c r="C122" t="n">
-        <v>2692.927042625093</v>
+        <v>2750.100252717521</v>
       </c>
       <c r="D122" t="n">
-        <v>3232.379939669494</v>
+        <v>3235.276668483668</v>
       </c>
       <c r="E122" t="n">
-        <v>2801.676025390625</v>
+        <v>3001.61376953125</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>45985</v>
+        <v>46013</v>
       </c>
       <c r="B123" t="n">
-        <v>2961.259429281129</v>
+        <v>2986.932815038227</v>
       </c>
       <c r="C123" t="n">
-        <v>2714.851204384922</v>
+        <v>2751.155186318953</v>
       </c>
       <c r="D123" t="n">
-        <v>3224.141276647319</v>
+        <v>3225.704390227548</v>
       </c>
       <c r="E123" t="n">
-        <v>2952.71337890625</v>
+        <v>3006.07373046875</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>45986</v>
+        <v>46014</v>
       </c>
       <c r="B124" t="n">
-        <v>2954.982734808942</v>
+        <v>2971.932472590171</v>
       </c>
       <c r="C124" t="n">
-        <v>2664.990110956503</v>
+        <v>2741.390255166617</v>
       </c>
       <c r="D124" t="n">
-        <v>3215.137735591964</v>
+        <v>3211.93557543443</v>
       </c>
       <c r="E124" t="n">
-        <v>2957.936279296875</v>
+        <v>2963.3740234375</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>45987</v>
+        <v>46015</v>
       </c>
       <c r="B125" t="n">
-        <v>2977.398971453989</v>
+        <v>2980.811006242059</v>
       </c>
       <c r="C125" t="n">
-        <v>2699.572660053263</v>
+        <v>2737.175940783708</v>
       </c>
       <c r="D125" t="n">
-        <v>3240.991595531662</v>
+        <v>3227.963954557863</v>
       </c>
       <c r="E125" t="n">
-        <v>3027.81201171875</v>
+        <v>2945.590576171875</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>45988</v>
+        <v>46016</v>
       </c>
       <c r="B126" t="n">
-        <v>2941.947765419967</v>
+        <v>2939.838604090667</v>
       </c>
       <c r="C126" t="n">
-        <v>2675.793057905097</v>
+        <v>2698.38890411794</v>
       </c>
       <c r="D126" t="n">
-        <v>3192.488156076314</v>
+        <v>3193.209747715469</v>
       </c>
       <c r="E126" t="n">
-        <v>3014.542236328125</v>
+        <v>2903.57958984375</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>45989</v>
+        <v>46017</v>
       </c>
       <c r="B127" t="n">
-        <v>2957.095862104556</v>
+        <v>2939.562020055551</v>
       </c>
       <c r="C127" t="n">
-        <v>2694.983082352975</v>
+        <v>2704.626119383836</v>
       </c>
       <c r="D127" t="n">
-        <v>3213.484016550443</v>
+        <v>3171.224209460739</v>
       </c>
       <c r="E127" t="n">
-        <v>3032.304443359375</v>
+        <v>2925.74560546875</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>45990</v>
+        <v>46018</v>
       </c>
       <c r="B128" t="n">
-        <v>2976.503332506539</v>
+        <v>2943.532600549528</v>
       </c>
       <c r="C128" t="n">
-        <v>2705.912571181772</v>
+        <v>2720.207901003538</v>
       </c>
       <c r="D128" t="n">
-        <v>3226.145360066439</v>
+        <v>3189.44854903162</v>
       </c>
       <c r="E128" t="n">
-        <v>2991.685302734375</v>
+        <v>2947.998291015625</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>45991</v>
+        <v>46019</v>
       </c>
       <c r="B129" t="n">
-        <v>3011.471220077963</v>
+        <v>2971.216742814724</v>
       </c>
       <c r="C129" t="n">
-        <v>2751.015813554749</v>
+        <v>2717.088834000764</v>
       </c>
       <c r="D129" t="n">
-        <v>3288.598234023586</v>
+        <v>3208.037048345902</v>
       </c>
       <c r="E129" t="n">
-        <v>2992.112548828125</v>
+        <v>2948.568115234375</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>45992</v>
+        <v>46020</v>
       </c>
       <c r="B130" t="n">
-        <v>3026.957946308512</v>
+        <v>2977.025761882863</v>
       </c>
       <c r="C130" t="n">
-        <v>2770.910924683364</v>
+        <v>2735.17196622816</v>
       </c>
       <c r="D130" t="n">
-        <v>3288.454977957869</v>
+        <v>3198.693580560082</v>
       </c>
       <c r="E130" t="n">
-        <v>2800.18896484375</v>
+        <v>2934.538330078125</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>45993</v>
+        <v>46021</v>
       </c>
       <c r="B131" t="n">
-        <v>3033.046275179608</v>
+        <v>2981.509371092152</v>
       </c>
       <c r="C131" t="n">
-        <v>2769.567217219566</v>
+        <v>2750.131743272867</v>
       </c>
       <c r="D131" t="n">
-        <v>3279.076488897216</v>
+        <v>3220.689929391845</v>
       </c>
       <c r="E131" t="n">
-        <v>2997.939697265625</v>
+        <v>2971.416748046875</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>45994</v>
+        <v>46022</v>
       </c>
       <c r="B132" t="n">
-        <v>3064.114073589216</v>
+        <v>3010.821024541517</v>
       </c>
       <c r="C132" t="n">
-        <v>2802.842091098745</v>
+        <v>2756.751044373848</v>
       </c>
       <c r="D132" t="n">
-        <v>3331.586346682937</v>
+        <v>3249.160041468354</v>
       </c>
       <c r="E132" t="n">
-        <v>3191.57177734375</v>
+        <v>2967.03759765625</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>45995</v>
+        <v>46023</v>
       </c>
       <c r="B133" t="n">
-        <v>3033.54226466378</v>
+        <v>2990.649675976531</v>
       </c>
       <c r="C133" t="n">
-        <v>2766.307725335028</v>
+        <v>2768.824874101926</v>
       </c>
       <c r="D133" t="n">
-        <v>3318.629061828417</v>
+        <v>3228.469457671229</v>
       </c>
       <c r="E133" t="n">
-        <v>3134.31640625</v>
+        <v>3000.394287109375</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>45996</v>
+        <v>46024</v>
       </c>
       <c r="B134" t="n">
-        <v>3049.83547240292</v>
+        <v>3010.931629221587</v>
       </c>
       <c r="C134" t="n">
-        <v>2786.069503624261</v>
+        <v>2769.820724158266</v>
       </c>
       <c r="D134" t="n">
-        <v>3329.934105426442</v>
+        <v>3228.295260667134</v>
       </c>
       <c r="E134" t="n">
-        <v>3024.432861328125</v>
+        <v>3124.422607421875</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>45997</v>
+        <v>46025</v>
       </c>
       <c r="B135" t="n">
-        <v>3066.787217912794</v>
+        <v>3034.593984852816</v>
       </c>
       <c r="C135" t="n">
-        <v>2793.874761079422</v>
+        <v>2795.695391044017</v>
       </c>
       <c r="D135" t="n">
-        <v>3352.471412746452</v>
+        <v>3276.077972113199</v>
       </c>
       <c r="E135" t="n">
-        <v>3040.207763671875</v>
+        <v>3125.91748046875</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>45998</v>
+        <v>46026</v>
       </c>
       <c r="B136" t="n">
-        <v>3095.924019873494</v>
+        <v>3080.481027599792</v>
       </c>
       <c r="C136" t="n">
-        <v>2823.308235987291</v>
+        <v>2865.152102190131</v>
       </c>
       <c r="D136" t="n">
-        <v>3353.144568313262</v>
+        <v>3300.94503148855</v>
       </c>
       <c r="E136" t="n">
-        <v>3061.3017578125</v>
+        <v>3140.71044921875</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>45999</v>
+        <v>46027</v>
       </c>
       <c r="B137" t="n">
-        <v>3102.515800281693</v>
+        <v>3102.400124504963</v>
       </c>
       <c r="C137" t="n">
-        <v>2840.594723754915</v>
+        <v>2875.905436594757</v>
       </c>
       <c r="D137" t="n">
-        <v>3392.676551693567</v>
+        <v>3330.928306024033</v>
       </c>
       <c r="E137" t="n">
-        <v>3125.197998046875</v>
+        <v>3226.13037109375</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46000</v>
+        <v>46028</v>
       </c>
       <c r="B138" t="n">
-        <v>3097.034544670629</v>
+        <v>3120.330927783398</v>
       </c>
       <c r="C138" t="n">
-        <v>2823.729443500595</v>
+        <v>2861.428201574598</v>
       </c>
       <c r="D138" t="n">
-        <v>3350.725408677561</v>
+        <v>3349.762458663641</v>
       </c>
       <c r="E138" t="n">
-        <v>3321.114990234375</v>
+        <v>3295.94677734375</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46001</v>
+        <v>46029</v>
       </c>
       <c r="B139" t="n">
-        <v>3114.314664733586</v>
+        <v>3159.90572673399</v>
       </c>
       <c r="C139" t="n">
-        <v>2858.637238649836</v>
+        <v>2925.278419601387</v>
       </c>
       <c r="D139" t="n">
-        <v>3371.310704095768</v>
+        <v>3406.571989709828</v>
       </c>
       <c r="E139" t="n">
-        <v>3325.39013671875</v>
+        <v>3166.843994140625</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46002</v>
+        <v>46030</v>
       </c>
       <c r="B140" t="n">
-        <v>3068.248729513175</v>
+        <v>3146.355116082802</v>
       </c>
       <c r="C140" t="n">
-        <v>2802.288139024706</v>
+        <v>2894.32467405777</v>
       </c>
       <c r="D140" t="n">
-        <v>3337.473768137206</v>
+        <v>3386.37229492404</v>
       </c>
       <c r="E140" t="n">
-        <v>3237.056884765625</v>
+        <v>3104.382568359375</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46003</v>
+        <v>46031</v>
       </c>
       <c r="B141" t="n">
-        <v>3067.894380564118</v>
+        <v>3169.232296928347</v>
       </c>
       <c r="C141" t="n">
-        <v>2813.130490748789</v>
+        <v>2930.758142395037</v>
       </c>
       <c r="D141" t="n">
-        <v>3315.334760238729</v>
+        <v>3409.650254626827</v>
       </c>
       <c r="E141" t="n">
-        <v>3084.172607421875</v>
+        <v>3083.047119140625</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46004</v>
+        <v>46032</v>
       </c>
       <c r="B142" t="n">
-        <v>3067.624651203699</v>
+        <v>3191.167192532563</v>
       </c>
       <c r="C142" t="n">
-        <v>2825.426504639795</v>
+        <v>2976.647717650132</v>
       </c>
       <c r="D142" t="n">
-        <v>3345.813245697571</v>
+        <v>3441.920291711555</v>
       </c>
       <c r="E142" t="n">
-        <v>3116.6953125</v>
+        <v>3082.39599609375</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46005</v>
+        <v>46033</v>
       </c>
       <c r="B143" t="n">
-        <v>3079.556433828238</v>
+        <v>3230.801446619277</v>
       </c>
       <c r="C143" t="n">
-        <v>2825.881141599392</v>
+        <v>2997.093481192401</v>
       </c>
       <c r="D143" t="n">
-        <v>3339.674170808962</v>
+        <v>3463.056035793299</v>
       </c>
       <c r="E143" t="n">
-        <v>3060.5947265625</v>
+        <v>3118.88525390625</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46006</v>
+        <v>46034</v>
       </c>
       <c r="B144" t="n">
-        <v>3069.544907249886</v>
+        <v>3241.840649796374</v>
       </c>
       <c r="C144" t="n">
-        <v>2796.028856348725</v>
+        <v>2987.679030929054</v>
       </c>
       <c r="D144" t="n">
-        <v>3345.629009542935</v>
+        <v>3472.795378353151</v>
       </c>
       <c r="E144" t="n">
-        <v>2964.18310546875</v>
+        <v>3092.3251953125</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46007</v>
+        <v>46035</v>
       </c>
       <c r="B145" t="n">
-        <v>3048.626299108083</v>
+        <v>3244.26742253998</v>
       </c>
       <c r="C145" t="n">
-        <v>2798.094996083029</v>
+        <v>2990.5307521139</v>
       </c>
       <c r="D145" t="n">
-        <v>3319.312248646712</v>
+        <v>3491.618048669376</v>
       </c>
       <c r="E145" t="n">
-        <v>2964.180908203125</v>
+        <v>3322.095458984375</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46008</v>
+        <v>46036</v>
       </c>
       <c r="B146" t="n">
-        <v>3052.16284994524</v>
+        <v>3263.823095697348</v>
       </c>
       <c r="C146" t="n">
-        <v>2802.953738976778</v>
+        <v>3019.857135009047</v>
       </c>
       <c r="D146" t="n">
-        <v>3325.961566969996</v>
+        <v>3525.563903584225</v>
       </c>
       <c r="E146" t="n">
-        <v>2831.403564453125</v>
+        <v>3354.72265625</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46009</v>
+        <v>46037</v>
       </c>
       <c r="B147" t="n">
-        <v>2994.524056098686</v>
+        <v>3225.952118268433</v>
       </c>
       <c r="C147" t="n">
-        <v>2736.51077442381</v>
+        <v>2984.477523235469</v>
       </c>
       <c r="D147" t="n">
-        <v>3260.140893445423</v>
+        <v>3464.551418053266</v>
       </c>
       <c r="E147" t="n">
-        <v>2827.069091796875</v>
+        <v>3317.101318359375</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46010</v>
+        <v>46038</v>
       </c>
       <c r="B148" t="n">
-        <v>2985.180392672452</v>
+        <v>3220.522537010495</v>
       </c>
       <c r="C148" t="n">
-        <v>2706.026812824572</v>
+        <v>2982.167595519266</v>
       </c>
       <c r="D148" t="n">
-        <v>3237.506865557898</v>
+        <v>3460.023742432207</v>
       </c>
       <c r="E148" t="n">
-        <v>2977.970703125</v>
+        <v>3295.482177734375</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46011</v>
+        <v>46039</v>
       </c>
       <c r="B149" t="n">
-        <v>2978.842089257195</v>
+        <v>3210.573823810492</v>
       </c>
       <c r="C149" t="n">
-        <v>2710.125585012413</v>
+        <v>2962.777178784874</v>
       </c>
       <c r="D149" t="n">
-        <v>3240.616337485581</v>
+        <v>3453.008901008485</v>
       </c>
       <c r="E149" t="n">
-        <v>2977.58251953125</v>
+        <v>3308.8642578125</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46012</v>
+        <v>46040</v>
       </c>
       <c r="B150" t="n">
-        <v>2987.87801156094</v>
+        <v>3215.24327484318</v>
       </c>
       <c r="C150" t="n">
-        <v>2711.881082405922</v>
+        <v>2981.077114668948</v>
       </c>
       <c r="D150" t="n">
-        <v>3258.246241567332</v>
+        <v>3444.46213454762</v>
       </c>
       <c r="E150" t="n">
-        <v>3001.61376953125</v>
+        <v>3281.15771484375</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46013</v>
+        <v>46041</v>
       </c>
       <c r="B151" t="n">
-        <v>2978.302720623403</v>
+        <v>3188.807542096019</v>
       </c>
       <c r="C151" t="n">
-        <v>2711.943500361744</v>
+        <v>2978.122895484722</v>
       </c>
       <c r="D151" t="n">
-        <v>3239.162251923834</v>
+        <v>3442.112302746337</v>
       </c>
       <c r="E151" t="n">
-        <v>3006.07373046875</v>
+        <v>3186.62109375</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46014</v>
+        <v>46042</v>
       </c>
       <c r="B152" t="n">
-        <v>2961.214281530379</v>
+        <v>3151.883192862615</v>
       </c>
       <c r="C152" t="n">
-        <v>2707.495122882342</v>
+        <v>2902.193206160659</v>
       </c>
       <c r="D152" t="n">
-        <v>3234.818938665815</v>
+        <v>3387.955815862443</v>
       </c>
       <c r="E152" t="n">
-        <v>2963.3740234375</v>
+        <v>2935.605712890625</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46015</v>
+        <v>46043</v>
       </c>
       <c r="B153" t="n">
-        <v>2971.936827728977</v>
+        <v>3130.894351431766</v>
       </c>
       <c r="C153" t="n">
-        <v>2732.411244915128</v>
+        <v>2886.552293115566</v>
       </c>
       <c r="D153" t="n">
-        <v>3235.45581312406</v>
+        <v>3374.535411272085</v>
       </c>
       <c r="E153" t="n">
-        <v>2945.590576171875</v>
+        <v>2978.901123046875</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46016</v>
+        <v>46044</v>
       </c>
       <c r="B154" t="n">
-        <v>2924.702543486416</v>
+        <v>3052.00190275114</v>
       </c>
       <c r="C154" t="n">
-        <v>2653.656247374005</v>
+        <v>2815.272961513489</v>
       </c>
       <c r="D154" t="n">
-        <v>3185.397558847981</v>
+        <v>3294.668674217271</v>
       </c>
       <c r="E154" t="n">
-        <v>2903.57958984375</v>
+        <v>2949.63330078125</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46017</v>
+        <v>46045</v>
       </c>
       <c r="B155" t="n">
-        <v>2928.746678072524</v>
+        <v>3005.807980703951</v>
       </c>
       <c r="C155" t="n">
-        <v>2680.611983933052</v>
+        <v>2780.184556701984</v>
       </c>
       <c r="D155" t="n">
-        <v>3197.554619053779</v>
+        <v>3231.573673571156</v>
       </c>
       <c r="E155" t="n">
-        <v>2925.74560546875</v>
+        <v>2953.25634765625</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46018</v>
+        <v>46046</v>
       </c>
       <c r="B156" t="n">
-        <v>2938.45327238187</v>
+        <v>2956.087413130047</v>
       </c>
       <c r="C156" t="n">
-        <v>2682.794587245363</v>
+        <v>2714.185431917396</v>
       </c>
       <c r="D156" t="n">
-        <v>3214.52775187547</v>
+        <v>3201.426240418073</v>
       </c>
       <c r="E156" t="n">
-        <v>2947.998291015625</v>
+        <v>2948.74072265625</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46019</v>
+        <v>46047</v>
       </c>
       <c r="B157" t="n">
-        <v>2965.781338928388</v>
+        <v>2922.697751296595</v>
       </c>
       <c r="C157" t="n">
-        <v>2686.105120055576</v>
+        <v>2707.071387507806</v>
       </c>
       <c r="D157" t="n">
-        <v>3229.5740315814</v>
+        <v>3170.41185154152</v>
       </c>
       <c r="E157" t="n">
-        <v>2948.568115234375</v>
+        <v>2815.90234375</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46020</v>
+        <v>46048</v>
       </c>
       <c r="B158" t="n">
-        <v>2976.261956257455</v>
+        <v>2860.604845368037</v>
       </c>
       <c r="C158" t="n">
-        <v>2711.885648359627</v>
+        <v>2615.121917374168</v>
       </c>
       <c r="D158" t="n">
-        <v>3212.551342177877</v>
+        <v>3111.309423656835</v>
       </c>
       <c r="E158" t="n">
-        <v>2934.538330078125</v>
+        <v>2926.45703125</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46021</v>
+        <v>46049</v>
       </c>
       <c r="B159" t="n">
-        <v>2980.448075103215</v>
+        <v>2791.068249223366</v>
       </c>
       <c r="C159" t="n">
-        <v>2695.917510772955</v>
+        <v>2544.450872216981</v>
       </c>
       <c r="D159" t="n">
-        <v>3240.160178304209</v>
+        <v>3006.628408355406</v>
       </c>
       <c r="E159" t="n">
-        <v>2971.416748046875</v>
+        <v>3022.2109375</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46022</v>
+        <v>46050</v>
       </c>
       <c r="B160" t="n">
-        <v>3013.070734373963</v>
+        <v>2741.094873504458</v>
       </c>
       <c r="C160" t="n">
-        <v>2746.297709208482</v>
+        <v>2508.781683210174</v>
       </c>
       <c r="D160" t="n">
-        <v>3272.148921960278</v>
+        <v>2975.737035316271</v>
       </c>
       <c r="E160" t="n">
-        <v>2967.03759765625</v>
+        <v>3006.607421875</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46023</v>
+        <v>46051</v>
       </c>
       <c r="B161" t="n">
-        <v>2987.735480971442</v>
+        <v>2637.35569898847</v>
       </c>
       <c r="C161" t="n">
-        <v>2725.251471903379</v>
+        <v>2407.414432604735</v>
       </c>
       <c r="D161" t="n">
-        <v>3251.083700165158</v>
+        <v>2882.259737506865</v>
       </c>
       <c r="E161" t="n">
-        <v>3000.394287109375</v>
+        <v>2818.232666015625</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46024</v>
+        <v>46052</v>
       </c>
       <c r="B162" t="n">
-        <v>3013.034810951833</v>
+        <v>2570.879564641972</v>
       </c>
       <c r="C162" t="n">
-        <v>2728.995471426339</v>
+        <v>2340.247525808501</v>
       </c>
       <c r="D162" t="n">
-        <v>3278.153686095778</v>
+        <v>2813.307310426606</v>
       </c>
       <c r="E162" t="n">
-        <v>3124.422607421875</v>
+        <v>2702.375244140625</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46025</v>
+        <v>46053</v>
       </c>
       <c r="B163" t="n">
-        <v>3042.708728427065</v>
+        <v>2505.775946281432</v>
       </c>
       <c r="C163" t="n">
-        <v>2783.503607316777</v>
+        <v>2271.814765474086</v>
       </c>
       <c r="D163" t="n">
-        <v>3316.620463326509</v>
+        <v>2770.450325132223</v>
       </c>
       <c r="E163" t="n">
-        <v>3125.91748046875</v>
+        <v>2445.091796875</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46026</v>
+        <v>46054</v>
       </c>
       <c r="B164" t="n">
-        <v>3088.087919558196</v>
+        <v>2462.138543834118</v>
       </c>
       <c r="C164" t="n">
-        <v>2823.200837616203</v>
+        <v>2222.446819171651</v>
       </c>
       <c r="D164" t="n">
-        <v>3363.70182815103</v>
+        <v>2685.851941069636</v>
       </c>
       <c r="E164" t="n">
-        <v>3140.71044921875</v>
+        <v>2267.96484375</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46027</v>
+        <v>46055</v>
       </c>
       <c r="B165" t="n">
-        <v>3114.106992721703</v>
+        <v>2395.066770903079</v>
       </c>
       <c r="C165" t="n">
-        <v>2858.662667259692</v>
+        <v>2151.001132209337</v>
       </c>
       <c r="D165" t="n">
-        <v>3374.762414463076</v>
+        <v>2645.120488886181</v>
       </c>
       <c r="E165" t="n">
-        <v>3226.13037109375</v>
+        <v>2344.356689453125</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46028</v>
+        <v>46056</v>
       </c>
       <c r="B166" t="n">
-        <v>3130.769687954895</v>
+        <v>2325.849501354325</v>
       </c>
       <c r="C166" t="n">
-        <v>2879.3506911184</v>
+        <v>2076.372644872835</v>
       </c>
       <c r="D166" t="n">
-        <v>3376.054752307947</v>
+        <v>2569.219603036298</v>
       </c>
       <c r="E166" t="n">
-        <v>3295.94677734375</v>
+        <v>2227.558837890625</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46029</v>
+        <v>46057</v>
       </c>
       <c r="B167" t="n">
-        <v>3172.319361325295</v>
+        <v>2281.419501216412</v>
       </c>
       <c r="C167" t="n">
-        <v>2906.771726557284</v>
+        <v>2048.974490465097</v>
       </c>
       <c r="D167" t="n">
-        <v>3420.504655600171</v>
+        <v>2511.419604967753</v>
       </c>
       <c r="E167" t="n">
-        <v>3166.843994140625</v>
+        <v>2143.504150390625</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="B168" t="n">
-        <v>3151.948178618514</v>
+        <v>2188.273305818919</v>
       </c>
       <c r="C168" t="n">
-        <v>2896.091682800643</v>
+        <v>1953.796174434379</v>
       </c>
       <c r="D168" t="n">
-        <v>3424.149407682309</v>
+        <v>2416.089910294859</v>
       </c>
       <c r="E168" t="n">
-        <v>3104.382568359375</v>
+        <v>1821.68310546875</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46031</v>
+        <v>46059</v>
       </c>
       <c r="B169" t="n">
-        <v>3177.920512975327</v>
+        <v>2137.17044507461</v>
       </c>
       <c r="C169" t="n">
-        <v>2914.7619299239</v>
+        <v>1885.522419952971</v>
       </c>
       <c r="D169" t="n">
-        <v>3454.343861997981</v>
+        <v>2358.500917548086</v>
       </c>
       <c r="E169" t="n">
-        <v>3083.047119140625</v>
+        <v>2063.386962890625</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46032</v>
+        <v>46060</v>
       </c>
       <c r="B170" t="n">
-        <v>3203.742370291596</v>
+        <v>2091.863765563645</v>
       </c>
       <c r="C170" t="n">
-        <v>2927.542417247033</v>
+        <v>1838.101675114027</v>
       </c>
       <c r="D170" t="n">
-        <v>3462.712532290137</v>
+        <v>2319.356733396357</v>
       </c>
       <c r="E170" t="n">
-        <v>3082.39599609375</v>
+        <v>2090.54931640625</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46033</v>
+        <v>46061</v>
       </c>
       <c r="B171" t="n">
-        <v>3240.611121069908</v>
+        <v>2072.012449533305</v>
       </c>
       <c r="C171" t="n">
-        <v>2973.335789052545</v>
+        <v>1853.612981489875</v>
       </c>
       <c r="D171" t="n">
-        <v>3490.8828467348</v>
+        <v>2313.254017907414</v>
       </c>
       <c r="E171" t="n">
-        <v>3118.88525390625</v>
+        <v>2088.762939453125</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46034</v>
+        <v>46062</v>
       </c>
       <c r="B172" t="n">
-        <v>3253.432831493531</v>
+        <v>2032.214562348307</v>
       </c>
       <c r="C172" t="n">
-        <v>2976.796604826137</v>
+        <v>1786.164369190489</v>
       </c>
       <c r="D172" t="n">
-        <v>3509.958214063086</v>
+        <v>2274.714512287321</v>
       </c>
       <c r="E172" t="n">
-        <v>3092.3251953125</v>
+        <v>2103.567626953125</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46035</v>
+        <v>46063</v>
       </c>
       <c r="B173" t="n">
-        <v>3252.289002294413</v>
+        <v>1993.203184114482</v>
       </c>
       <c r="C173" t="n">
-        <v>2990.494570469182</v>
+        <v>1764.677051116855</v>
       </c>
       <c r="D173" t="n">
-        <v>3504.558113036697</v>
+        <v>2223.395252580406</v>
       </c>
       <c r="E173" t="n">
-        <v>3322.095458984375</v>
+        <v>2019.497436523438</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46036</v>
+        <v>46064</v>
       </c>
       <c r="B174" t="n">
-        <v>3271.605993388201</v>
+        <v>1981.314226255746</v>
       </c>
       <c r="C174" t="n">
-        <v>2994.3714667906</v>
+        <v>1734.85995951712</v>
       </c>
       <c r="D174" t="n">
-        <v>3551.463530119219</v>
+        <v>2199.403020239973</v>
       </c>
       <c r="E174" t="n">
-        <v>3354.72265625</v>
+        <v>1940.621337890625</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46037</v>
+        <v>46065</v>
       </c>
       <c r="B175" t="n">
-        <v>3224.860604875351</v>
+        <v>1922.420346016146</v>
       </c>
       <c r="C175" t="n">
-        <v>2969.406145046896</v>
+        <v>1665.709645738181</v>
       </c>
       <c r="D175" t="n">
-        <v>3500.443623961483</v>
+        <v>2161.90802697809</v>
       </c>
       <c r="E175" t="n">
-        <v>3317.101318359375</v>
+        <v>1946.940673828125</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46038</v>
+        <v>46066</v>
       </c>
       <c r="B176" t="n">
-        <v>3220.697413017735</v>
+        <v>1906.644504577104</v>
       </c>
       <c r="C176" t="n">
-        <v>2939.689546190746</v>
+        <v>1666.783907409999</v>
       </c>
       <c r="D176" t="n">
-        <v>3486.284252264703</v>
+        <v>2148.455186673097</v>
       </c>
       <c r="E176" t="n">
-        <v>3295.482177734375</v>
+        <v>2048.52734375</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46039</v>
+        <v>46067</v>
       </c>
       <c r="B177" t="n">
-        <v>3213.08984816338</v>
+        <v>1897.104559662733</v>
       </c>
       <c r="C177" t="n">
-        <v>2954.339583369027</v>
+        <v>1660.57180876688</v>
       </c>
       <c r="D177" t="n">
-        <v>3482.959813198924</v>
+        <v>2140.637595315085</v>
       </c>
       <c r="E177" t="n">
-        <v>3308.8642578125</v>
+        <v>2086.009765625</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46040</v>
+        <v>46068</v>
       </c>
       <c r="B178" t="n">
-        <v>3213.779513990551</v>
+        <v>1912.84014316898</v>
       </c>
       <c r="C178" t="n">
-        <v>2937.002523953961</v>
+        <v>1692.397931068602</v>
       </c>
       <c r="D178" t="n">
-        <v>3478.848868582871</v>
+        <v>2145.439351607272</v>
       </c>
       <c r="E178" t="n">
-        <v>3281.15771484375</v>
+        <v>1966.04296875</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46041</v>
+        <v>46069</v>
       </c>
       <c r="B179" t="n">
-        <v>3188.281312474448</v>
+        <v>1907.858326265818</v>
       </c>
       <c r="C179" t="n">
-        <v>2928.744961785113</v>
+        <v>1674.319931245164</v>
       </c>
       <c r="D179" t="n">
-        <v>3448.969307382802</v>
+        <v>2150.154849356583</v>
       </c>
       <c r="E179" t="n">
-        <v>3186.62109375</v>
+        <v>1997.917724609375</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46042</v>
+        <v>46070</v>
       </c>
       <c r="B180" t="n">
-        <v>3147.33649611947</v>
+        <v>1902.34181770339</v>
       </c>
       <c r="C180" t="n">
-        <v>2893.19723728193</v>
+        <v>1669.638237235346</v>
       </c>
       <c r="D180" t="n">
-        <v>3426.555947772172</v>
+        <v>2137.272041512005</v>
       </c>
       <c r="E180" t="n">
-        <v>2935.605712890625</v>
+        <v>1992.1943359375</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46043</v>
+        <v>46071</v>
       </c>
       <c r="B181" t="n">
-        <v>3126.067274932197</v>
+        <v>1922.127528992369</v>
       </c>
       <c r="C181" t="n">
-        <v>2855.810898615171</v>
+        <v>1680.090696477702</v>
       </c>
       <c r="D181" t="n">
-        <v>3388.570298344802</v>
+        <v>2184.37980399856</v>
       </c>
       <c r="E181" t="n">
-        <v>2978.901123046875</v>
+        <v>1953.97412109375</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46044</v>
+        <v>46072</v>
       </c>
       <c r="B182" t="n">
-        <v>3038.666821621874</v>
+        <v>1892.649685431803</v>
       </c>
       <c r="C182" t="n">
-        <v>2779.834532668083</v>
+        <v>1646.762484023442</v>
       </c>
       <c r="D182" t="n">
-        <v>3308.320042045331</v>
+        <v>2129.870724001665</v>
       </c>
       <c r="E182" t="n">
-        <v>2949.63330078125</v>
+        <v>1948.201049804688</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46045</v>
+        <v>46073</v>
       </c>
       <c r="B183" t="n">
-        <v>2994.500662225033</v>
+        <v>1903.660842854709</v>
       </c>
       <c r="C183" t="n">
-        <v>2739.966572149645</v>
+        <v>1656.288683139907</v>
       </c>
       <c r="D183" t="n">
-        <v>3271.39158967422</v>
+        <v>2143.896782702105</v>
       </c>
       <c r="E183" t="n">
-        <v>2953.25634765625</v>
+        <v>1969.022338867188</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46046</v>
+        <v>46074</v>
       </c>
       <c r="B184" t="n">
-        <v>2948.25183245228</v>
+        <v>1917.98206403701</v>
       </c>
       <c r="C184" t="n">
-        <v>2677.618404801653</v>
+        <v>1691.074556347059</v>
       </c>
       <c r="D184" t="n">
-        <v>3197.061713425189</v>
+        <v>2157.23772814022</v>
       </c>
       <c r="E184" t="n">
-        <v>2948.74072265625</v>
+        <v>1973.737182617188</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46047</v>
+        <v>46075</v>
       </c>
       <c r="B185" t="n">
-        <v>2912.344687165218</v>
+        <v>1954.433420787634</v>
       </c>
       <c r="C185" t="n">
-        <v>2645.251323700873</v>
+        <v>1703.349570398526</v>
       </c>
       <c r="D185" t="n">
-        <v>3157.198876054525</v>
+        <v>2178.930703800745</v>
       </c>
       <c r="E185" t="n">
-        <v>2815.90234375</v>
+        <v>1957.805908203125</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46048</v>
+        <v>46076</v>
       </c>
       <c r="B186" t="n">
-        <v>2852.935299442554</v>
+        <v>1966.881289910991</v>
       </c>
       <c r="C186" t="n">
-        <v>2592.485039938907</v>
+        <v>1722.353916976118</v>
       </c>
       <c r="D186" t="n">
-        <v>3110.835525359918</v>
+        <v>2213.117931040509</v>
       </c>
       <c r="E186" t="n">
-        <v>2926.45703125</v>
+        <v>1855.502807617188</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46049</v>
+        <v>46077</v>
       </c>
       <c r="B187" t="n">
-        <v>2781.350919683739</v>
+        <v>1975.446214193324</v>
       </c>
       <c r="C187" t="n">
-        <v>2505.467931060527</v>
+        <v>1728.061839035807</v>
       </c>
       <c r="D187" t="n">
-        <v>3054.59947086309</v>
+        <v>2212.59225283713</v>
       </c>
       <c r="E187" t="n">
-        <v>3022.2109375</v>
+        <v>1852.969482421875</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46050</v>
+        <v>46078</v>
       </c>
       <c r="B188" t="n">
-        <v>2733.23243557553</v>
+        <v>2005.979229140857</v>
       </c>
       <c r="C188" t="n">
-        <v>2469.713388052297</v>
+        <v>1763.613164665753</v>
       </c>
       <c r="D188" t="n">
-        <v>2996.067608058356</v>
+        <v>2247.141777277366</v>
       </c>
       <c r="E188" t="n">
-        <v>3006.607421875</v>
+        <v>2054.6279296875</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46051</v>
+        <v>46079</v>
       </c>
       <c r="B189" t="n">
-        <v>2623.213950297558</v>
+        <v>1984.000956256765</v>
       </c>
       <c r="C189" t="n">
-        <v>2371.166724702043</v>
+        <v>1752.059522258022</v>
       </c>
       <c r="D189" t="n">
-        <v>2892.435000724867</v>
+        <v>2235.972466559395</v>
       </c>
       <c r="E189" t="n">
-        <v>2818.232666015625</v>
+        <v>2026.792602539062</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46052</v>
+        <v>46080</v>
       </c>
       <c r="B190" t="n">
-        <v>2561.015692145519</v>
+        <v>1999.416985303564</v>
       </c>
       <c r="C190" t="n">
-        <v>2300.189908198854</v>
+        <v>1739.734584914735</v>
       </c>
       <c r="D190" t="n">
-        <v>2836.173217205448</v>
+        <v>2239.264158059203</v>
       </c>
       <c r="E190" t="n">
-        <v>2702.375244140625</v>
+        <v>1930.761840820312</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B191" t="n">
-        <v>2501.582808843615</v>
+        <v>2015.261000192124</v>
       </c>
       <c r="C191" t="n">
-        <v>2221.138865123675</v>
+        <v>1773.678511011303</v>
       </c>
       <c r="D191" t="n">
-        <v>2770.330705555631</v>
+        <v>2247.376043898918</v>
       </c>
       <c r="E191" t="n">
-        <v>2445.091796875</v>
+        <v>1965.050537109375</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B192" t="n">
-        <v>2457.50505145761</v>
+        <v>2050.617047182718</v>
       </c>
       <c r="C192" t="n">
-        <v>2192.217724499315</v>
+        <v>1819.071299143733</v>
       </c>
       <c r="D192" t="n">
-        <v>2738.625292723383</v>
+        <v>2291.79941317275</v>
       </c>
       <c r="E192" t="n">
-        <v>2267.96484375</v>
+        <v>1939.066650390625</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46055</v>
+        <v>46083</v>
       </c>
       <c r="B193" t="n">
-        <v>2395.005343063496</v>
+        <v>2059.657670378077</v>
       </c>
       <c r="C193" t="n">
-        <v>2144.471998649446</v>
+        <v>1832.440376698262</v>
       </c>
       <c r="D193" t="n">
-        <v>2652.58204060108</v>
+        <v>2294.603449494426</v>
       </c>
       <c r="E193" t="n">
-        <v>2344.356689453125</v>
+        <v>2027.268920898438</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46056</v>
+        <v>46084</v>
       </c>
       <c r="B194" t="n">
-        <v>2325.379702766719</v>
+        <v>2062.841959356915</v>
       </c>
       <c r="C194" t="n">
-        <v>2065.93227555888</v>
+        <v>1811.948221722326</v>
       </c>
       <c r="D194" t="n">
-        <v>2576.202754200322</v>
+        <v>2311.36616968957</v>
       </c>
       <c r="E194" t="n">
-        <v>2227.558837890625</v>
+        <v>1982.768920898438</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46057</v>
+        <v>46085</v>
       </c>
       <c r="B195" t="n">
-        <v>2284.142408309298</v>
+        <v>2086.381692196026</v>
       </c>
       <c r="C195" t="n">
-        <v>2019.202913785283</v>
+        <v>1843.458831844695</v>
       </c>
       <c r="D195" t="n">
-        <v>2531.45710382689</v>
+        <v>2338.797488021876</v>
       </c>
       <c r="E195" t="n">
-        <v>2143.504150390625</v>
+        <v>2126.50537109375</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46058</v>
+        <v>46086</v>
       </c>
       <c r="B196" t="n">
-        <v>2185.710401977638</v>
+        <v>2056.170158040444</v>
       </c>
       <c r="C196" t="n">
-        <v>1934.529754901053</v>
+        <v>1813.131420153276</v>
       </c>
       <c r="D196" t="n">
-        <v>2435.216049532425</v>
+        <v>2306.253681386527</v>
       </c>
       <c r="E196" t="n">
-        <v>1821.68310546875</v>
+        <v>2071.60546875</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46059</v>
+        <v>46087</v>
       </c>
       <c r="B197" t="n">
-        <v>2139.502988995977</v>
+        <v>2062.487457917006</v>
       </c>
       <c r="C197" t="n">
-        <v>1891.903254745799</v>
+        <v>1838.978966977473</v>
       </c>
       <c r="D197" t="n">
-        <v>2383.576498897499</v>
+        <v>2308.993882893298</v>
       </c>
       <c r="E197" t="n">
-        <v>2063.386962890625</v>
+        <v>1978.751220703125</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46060</v>
+        <v>46088</v>
       </c>
       <c r="B198" t="n">
-        <v>2100.089172392512</v>
+        <v>2068.734000514334</v>
       </c>
       <c r="C198" t="n">
-        <v>1837.066790809984</v>
+        <v>1799.572034459628</v>
       </c>
       <c r="D198" t="n">
-        <v>2363.86452957157</v>
+        <v>2289.863156370651</v>
       </c>
       <c r="E198" t="n">
-        <v>2090.54931640625</v>
+        <v>1969.455444335938</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46061</v>
+        <v>46089</v>
       </c>
       <c r="B199" t="n">
-        <v>2079.617379828233</v>
+        <v>2094.343831946802</v>
       </c>
       <c r="C199" t="n">
-        <v>1800.259398355642</v>
+        <v>1845.745552533079</v>
       </c>
       <c r="D199" t="n">
-        <v>2341.697593688078</v>
+        <v>2310.966946057345</v>
       </c>
       <c r="E199" t="n">
-        <v>2088.762939453125</v>
+        <v>1936.604736328125</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46062</v>
+        <v>46090</v>
       </c>
       <c r="B200" t="n">
-        <v>2043.815296569928</v>
+        <v>2093.814737662122</v>
       </c>
       <c r="C200" t="n">
-        <v>1792.302516411282</v>
+        <v>1854.000034114044</v>
       </c>
       <c r="D200" t="n">
-        <v>2318.267853772201</v>
+        <v>2336.855185528145</v>
       </c>
       <c r="E200" t="n">
-        <v>2103.567626953125</v>
+        <v>1992.938232421875</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46063</v>
+        <v>46091</v>
       </c>
       <c r="B201" t="n">
-        <v>2003.441977977291</v>
+        <v>2087.899341872093</v>
       </c>
       <c r="C201" t="n">
-        <v>1716.500384844007</v>
+        <v>1866.361225143523</v>
       </c>
       <c r="D201" t="n">
-        <v>2280.587070832139</v>
+        <v>2313.228805855253</v>
       </c>
       <c r="E201" t="n">
-        <v>2019.497436523438</v>
+        <v>2037.120483398438</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46064</v>
+        <v>46092</v>
       </c>
       <c r="B202" t="n">
-        <v>1993.445763925476</v>
+        <v>2103.065530938521</v>
       </c>
       <c r="C202" t="n">
-        <v>1733.011786416616</v>
+        <v>1855.688791179792</v>
       </c>
       <c r="D202" t="n">
-        <v>2274.850686887618</v>
+        <v>2345.456233203799</v>
       </c>
       <c r="E202" t="n">
-        <v>1940.621337890625</v>
+        <v>2051.5732421875</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46065</v>
+        <v>46093</v>
       </c>
       <c r="B203" t="n">
-        <v>1927.661752549155</v>
+        <v>2065.420889830449</v>
       </c>
       <c r="C203" t="n">
-        <v>1680.471868552692</v>
+        <v>1838.40801664757</v>
       </c>
       <c r="D203" t="n">
-        <v>2170.175580693244</v>
+        <v>2288.773348061902</v>
       </c>
       <c r="E203" t="n">
-        <v>1946.940673828125</v>
+        <v>2073.13623046875</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46066</v>
+        <v>46094</v>
       </c>
       <c r="B204" t="n">
-        <v>1914.924476774999</v>
+        <v>2065.415011814212</v>
       </c>
       <c r="C204" t="n">
-        <v>1656.207719931236</v>
+        <v>1827.840043862895</v>
       </c>
       <c r="D204" t="n">
-        <v>2171.420174732862</v>
+        <v>2302.09991737549</v>
       </c>
       <c r="E204" t="n">
-        <v>2048.52734375</v>
+        <v>2092.5634765625</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46067</v>
+        <v>46095</v>
       </c>
       <c r="B205" t="n">
-        <v>1909.227852660897</v>
+        <v>2066.571419056918</v>
       </c>
       <c r="C205" t="n">
-        <v>1648.119065021311</v>
+        <v>1826.436279602443</v>
       </c>
       <c r="D205" t="n">
-        <v>2172.860999388218</v>
+        <v>2324.576650846708</v>
       </c>
       <c r="E205" t="n">
-        <v>2086.009765625</v>
+        <v>2097.086669921875</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46068</v>
+        <v>46096</v>
       </c>
       <c r="B206" t="n">
-        <v>1922.166850439247</v>
+        <v>2088.400712205479</v>
       </c>
       <c r="C206" t="n">
-        <v>1664.428203102653</v>
+        <v>1849.356148437261</v>
       </c>
       <c r="D206" t="n">
-        <v>2178.267554004689</v>
+        <v>2330.888668756384</v>
       </c>
       <c r="E206" t="n">
-        <v>1966.04296875</v>
+        <v>2177.476318359375</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46069</v>
+        <v>46097</v>
       </c>
       <c r="B207" t="n">
-        <v>1918.948331701894</v>
+        <v>2085.431826840985</v>
       </c>
       <c r="C207" t="n">
-        <v>1645.363901001703</v>
+        <v>1841.972915000247</v>
       </c>
       <c r="D207" t="n">
-        <v>2191.772298286674</v>
+        <v>2340.333010814007</v>
       </c>
       <c r="E207" t="n">
-        <v>1997.917724609375</v>
+        <v>2351.176025390625</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46070</v>
+        <v>46098</v>
       </c>
       <c r="B208" t="n">
-        <v>1909.852979623268</v>
+        <v>2078.405525382334</v>
       </c>
       <c r="C208" t="n">
-        <v>1650.88690110788</v>
+        <v>1825.432016532698</v>
       </c>
       <c r="D208" t="n">
-        <v>2173.979130026481</v>
+        <v>2330.667037348003</v>
       </c>
       <c r="E208" t="n">
-        <v>1992.1943359375</v>
+        <v>2318.053466796875</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46071</v>
+        <v>46099</v>
       </c>
       <c r="B209" t="n">
-        <v>1929.401683992812</v>
+        <v>2093.738322217852</v>
       </c>
       <c r="C209" t="n">
-        <v>1677.709816384547</v>
+        <v>1840.623533166572</v>
       </c>
       <c r="D209" t="n">
-        <v>2187.300658801084</v>
+        <v>2339.150143954806</v>
       </c>
       <c r="E209" t="n">
-        <v>1953.97412109375</v>
+        <v>2203.671630859375</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46072</v>
+        <v>46100</v>
       </c>
       <c r="B210" t="n">
-        <v>1891.059899498908</v>
+        <v>2057.451373392385</v>
       </c>
       <c r="C210" t="n">
-        <v>1603.527605223585</v>
+        <v>1841.49974272721</v>
       </c>
       <c r="D210" t="n">
-        <v>2164.658640885153</v>
+        <v>2297.39320775294</v>
       </c>
       <c r="E210" t="n">
-        <v>1948.201049804688</v>
+        <v>2137.423828125</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46073</v>
+        <v>46101</v>
       </c>
       <c r="B211" t="n">
-        <v>1903.355587143818</v>
+        <v>2059.878013097254</v>
       </c>
       <c r="C211" t="n">
-        <v>1627.888298577714</v>
+        <v>1826.588584169236</v>
       </c>
       <c r="D211" t="n">
-        <v>2158.105024772836</v>
+        <v>2294.58562649526</v>
       </c>
       <c r="E211" t="n">
-        <v>1969.022338867188</v>
+        <v>2146.4970703125</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46074</v>
+        <v>46102</v>
       </c>
       <c r="B212" t="n">
-        <v>1920.042700635302</v>
+        <v>2064.401479138636</v>
       </c>
       <c r="C212" t="n">
-        <v>1645.327547515891</v>
+        <v>1815.387892330282</v>
       </c>
       <c r="D212" t="n">
-        <v>2182.907532903583</v>
+        <v>2286.072441866414</v>
       </c>
       <c r="E212" t="n">
-        <v>1973.737182617188</v>
+        <v>2076.68994140625</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46075</v>
+        <v>46103</v>
       </c>
       <c r="B213" t="n">
-        <v>1952.544656561794</v>
+        <v>2090.37424084209</v>
       </c>
       <c r="C213" t="n">
-        <v>1682.897982494979</v>
+        <v>1858.085261246693</v>
       </c>
       <c r="D213" t="n">
-        <v>2216.550510675161</v>
+        <v>2327.592767482607</v>
       </c>
       <c r="E213" t="n">
-        <v>1957.805908203125</v>
+        <v>2053.04833984375</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46076</v>
+        <v>46104</v>
       </c>
       <c r="B214" t="n">
-        <v>1965.965258417244</v>
+        <v>2092.155598997513</v>
       </c>
       <c r="C214" t="n">
-        <v>1719.245858538236</v>
+        <v>1841.127977605867</v>
       </c>
       <c r="D214" t="n">
-        <v>2217.891972778825</v>
+        <v>2342.711631089214</v>
       </c>
       <c r="E214" t="n">
-        <v>1855.502807617188</v>
+        <v>2152.14599609375</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46077</v>
+        <v>46105</v>
       </c>
       <c r="B215" t="n">
-        <v>1970.549070455255</v>
+        <v>2090.311482016418</v>
       </c>
       <c r="C215" t="n">
-        <v>1729.571916807875</v>
+        <v>1846.074388914852</v>
       </c>
       <c r="D215" t="n">
-        <v>2237.004255886657</v>
+        <v>2325.798658973338</v>
       </c>
       <c r="E215" t="n">
-        <v>1852.969482421875</v>
+        <v>2155.704345703125</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46078</v>
+        <v>46106</v>
       </c>
       <c r="B216" t="n">
-        <v>2000.844714861737</v>
+        <v>2111.084439908966</v>
       </c>
       <c r="C216" t="n">
-        <v>1748.467438480151</v>
+        <v>1852.969430459842</v>
       </c>
       <c r="D216" t="n">
-        <v>2274.459324877042</v>
+        <v>2345.863144347118</v>
       </c>
       <c r="E216" t="n">
-        <v>2054.6279296875</v>
+        <v>2168.021484375</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46079</v>
+        <v>46107</v>
       </c>
       <c r="B217" t="n">
-        <v>1970.404757162315</v>
+        <v>2080.328186963784</v>
       </c>
       <c r="C217" t="n">
-        <v>1703.328325416416</v>
+        <v>1834.781103192776</v>
       </c>
       <c r="D217" t="n">
-        <v>2246.703158329317</v>
+        <v>2317.750063427119</v>
       </c>
       <c r="E217" t="n">
-        <v>2026.792602539062</v>
+        <v>2059.578369140625</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46080</v>
+        <v>46108</v>
       </c>
       <c r="B218" t="n">
-        <v>1987.897967825896</v>
+        <v>2088.220214681012</v>
       </c>
       <c r="C218" t="n">
-        <v>1703.092621763083</v>
+        <v>1838.613059105777</v>
       </c>
       <c r="D218" t="n">
-        <v>2257.919990793383</v>
+        <v>2331.280123143847</v>
       </c>
       <c r="E218" t="n">
-        <v>1930.761840820312</v>
+        <v>1991.27197265625</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46081</v>
+        <v>46109</v>
       </c>
       <c r="B219" t="n">
-        <v>2007.266124940217</v>
+        <v>2098.003880888328</v>
       </c>
       <c r="C219" t="n">
-        <v>1761.374663934806</v>
+        <v>1865.956571822354</v>
       </c>
       <c r="D219" t="n">
-        <v>2256.594298470977</v>
+        <v>2325.468842729974</v>
       </c>
       <c r="E219" t="n">
-        <v>1965.050537109375</v>
+        <v>1992.694580078125</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46082</v>
+        <v>46110</v>
       </c>
       <c r="B220" t="n">
-        <v>2040.160018457258</v>
+        <v>2128.911280102404</v>
       </c>
       <c r="C220" t="n">
-        <v>1769.897751518835</v>
+        <v>1889.113942571398</v>
       </c>
       <c r="D220" t="n">
-        <v>2326.446478017936</v>
+        <v>2376.108523375858</v>
       </c>
       <c r="E220" t="n">
-        <v>1939.066650390625</v>
+        <v>1982.559692382812</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46083</v>
+        <v>46111</v>
       </c>
       <c r="B221" t="n">
-        <v>2051.942358907927</v>
+        <v>2135.203487080109</v>
       </c>
       <c r="C221" t="n">
-        <v>1778.949758086355</v>
+        <v>1892.31151370832</v>
       </c>
       <c r="D221" t="n">
-        <v>2329.484737540206</v>
+        <v>2376.982914698197</v>
       </c>
       <c r="E221" t="n">
-        <v>2027.268920898438</v>
+        <v>2023.514892578125</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46084</v>
+        <v>46112</v>
       </c>
       <c r="B222" t="n">
-        <v>2053.13982572749</v>
+        <v>2137.372051288046</v>
       </c>
       <c r="C222" t="n">
-        <v>1786.48039639287</v>
+        <v>1882.514597084176</v>
       </c>
       <c r="D222" t="n">
-        <v>2328.165689659636</v>
+        <v>2370.079442012756</v>
       </c>
       <c r="E222" t="n">
-        <v>1982.768920898438</v>
+        <v>2104.708251953125</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46085</v>
+        <v>46113</v>
       </c>
       <c r="B223" t="n">
-        <v>2078.597963800878</v>
+        <v>2161.609730936827</v>
       </c>
       <c r="C223" t="n">
-        <v>1814.731712966712</v>
+        <v>1927.171378953151</v>
       </c>
       <c r="D223" t="n">
-        <v>2356.971487271014</v>
+        <v>2394.132244918142</v>
       </c>
       <c r="E223" t="n">
-        <v>2126.50537109375</v>
+        <v>2138.737060546875</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46086</v>
+        <v>46114</v>
       </c>
       <c r="B224" t="n">
-        <v>2042.172821132149</v>
+        <v>2133.744835582665</v>
       </c>
       <c r="C224" t="n">
-        <v>1779.569632293687</v>
+        <v>1878.174986272585</v>
       </c>
       <c r="D224" t="n">
-        <v>2320.031808392339</v>
+        <v>2370.221153124824</v>
       </c>
       <c r="E224" t="n">
-        <v>2071.60546875</v>
+        <v>2056.8525390625</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46087</v>
+        <v>46115</v>
       </c>
       <c r="B225" t="n">
-        <v>2052.835328471775</v>
+        <v>2143.952748389279</v>
       </c>
       <c r="C225" t="n">
-        <v>1793.383650735709</v>
+        <v>1891.848872013368</v>
       </c>
       <c r="D225" t="n">
-        <v>2326.332321429014</v>
+        <v>2385.20898161677</v>
       </c>
       <c r="E225" t="n">
-        <v>1978.751220703125</v>
+        <v>2053.38525390625</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46088</v>
+        <v>46116</v>
       </c>
       <c r="B226" t="n">
-        <v>2064.820778065259</v>
+        <v>2155.496109735614</v>
       </c>
       <c r="C226" t="n">
-        <v>1794.810109814364</v>
+        <v>1928.539226245109</v>
       </c>
       <c r="D226" t="n">
-        <v>2322.555354167238</v>
+        <v>2421.725349680572</v>
       </c>
       <c r="E226" t="n">
-        <v>1969.455444335938</v>
+        <v>2065.3515625</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46089</v>
+        <v>46117</v>
       </c>
       <c r="B227" t="n">
-        <v>2090.058230046932</v>
+        <v>2187.645070026688</v>
       </c>
       <c r="C227" t="n">
-        <v>1843.55807848777</v>
+        <v>1950.127443080963</v>
       </c>
       <c r="D227" t="n">
-        <v>2360.387738885795</v>
+        <v>2422.964125210317</v>
       </c>
       <c r="E227" t="n">
-        <v>1936.604736328125</v>
+        <v>2108.99560546875</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46090</v>
+        <v>46118</v>
       </c>
       <c r="B228" t="n">
-        <v>2094.167688176298</v>
+        <v>2194.714325460588</v>
       </c>
       <c r="C228" t="n">
-        <v>1811.968653848269</v>
+        <v>1971.122292942855</v>
       </c>
       <c r="D228" t="n">
-        <v>2356.176574751662</v>
+        <v>2426.86975932622</v>
       </c>
       <c r="E228" t="n">
-        <v>1992.938232421875</v>
+        <v>2107.761474609375</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46091</v>
+        <v>46119</v>
       </c>
       <c r="B229" t="n">
-        <v>2087.907387463701</v>
+        <v>2197.260953172574</v>
       </c>
       <c r="C229" t="n">
-        <v>1832.475580659624</v>
+        <v>1960.351856477734</v>
       </c>
       <c r="D229" t="n">
-        <v>2356.95722930946</v>
+        <v>2436.713682325544</v>
       </c>
       <c r="E229" t="n">
-        <v>2037.120483398438</v>
+        <v>2241.806640625</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46092</v>
+        <v>46120</v>
       </c>
       <c r="B230" t="n">
-        <v>2106.32497623684</v>
+        <v>2221.551184217395</v>
       </c>
       <c r="C230" t="n">
-        <v>1858.426760781197</v>
+        <v>1996.990499627544</v>
       </c>
       <c r="D230" t="n">
-        <v>2396.029992581012</v>
+        <v>2454.100221158195</v>
       </c>
       <c r="E230" t="n">
-        <v>2051.5732421875</v>
+        <v>2190.33544921875</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46093</v>
+        <v>46121</v>
       </c>
       <c r="B231" t="n">
-        <v>2063.446525348297</v>
+        <v>2193.49063930644</v>
       </c>
       <c r="C231" t="n">
-        <v>1811.25396754791</v>
+        <v>1946.812876560601</v>
       </c>
       <c r="D231" t="n">
-        <v>2317.635496781182</v>
+        <v>2441.403327966531</v>
       </c>
       <c r="E231" t="n">
-        <v>2073.13623046875</v>
+        <v>2189.14404296875</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46094</v>
+        <v>46122</v>
       </c>
       <c r="B232" t="n">
-        <v>2068.379371037521</v>
+        <v>2203.331754318376</v>
       </c>
       <c r="C232" t="n">
-        <v>1790.592070466906</v>
+        <v>1951.630107384649</v>
       </c>
       <c r="D232" t="n">
-        <v>2340.740740964005</v>
+        <v>2437.012557323888</v>
       </c>
       <c r="E232" t="n">
-        <v>2092.5634765625</v>
+        <v>2245.148681640625</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46095</v>
+        <v>46123</v>
       </c>
       <c r="B233" t="n">
-        <v>2075.461122151532</v>
+        <v>2214.410030384986</v>
       </c>
       <c r="C233" t="n">
-        <v>1795.604608367522</v>
+        <v>1993.69905690746</v>
       </c>
       <c r="D233" t="n">
-        <v>2328.854218506475</v>
+        <v>2457.849329917082</v>
       </c>
       <c r="E233" t="n">
-        <v>2097.086669921875</v>
+        <v>2285.39013671875</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46096</v>
+        <v>46124</v>
       </c>
       <c r="B234" t="n">
-        <v>2096.68960273081</v>
+        <v>2246.060657704573</v>
       </c>
       <c r="C234" t="n">
-        <v>1832.59125736113</v>
+        <v>2020.879753199041</v>
       </c>
       <c r="D234" t="n">
-        <v>2369.17681901719</v>
+        <v>2498.301407691103</v>
       </c>
       <c r="E234" t="n">
-        <v>2177.476318359375</v>
+        <v>2192.201171875</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46097</v>
+        <v>46125</v>
       </c>
       <c r="B235" t="n">
-        <v>2097.721487297313</v>
+        <v>2252.652355785406</v>
       </c>
       <c r="C235" t="n">
-        <v>1848.271514434869</v>
+        <v>2010.685221261677</v>
       </c>
       <c r="D235" t="n">
-        <v>2385.252021214105</v>
+        <v>2474.396029460815</v>
       </c>
       <c r="E235" t="n">
-        <v>2351.176025390625</v>
+        <v>2370.71484375</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46098</v>
+        <v>46126</v>
       </c>
       <c r="B236" t="n">
-        <v>2089.321863315502</v>
+        <v>2254.782556685691</v>
       </c>
       <c r="C236" t="n">
-        <v>1830.173597792977</v>
+        <v>2004.234896457715</v>
       </c>
       <c r="D236" t="n">
-        <v>2356.002786823084</v>
+        <v>2485.28884020814</v>
       </c>
       <c r="E236" t="n">
-        <v>2318.053466796875</v>
+        <v>2323.30859375</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46099</v>
+        <v>46127</v>
       </c>
       <c r="B237" t="n">
-        <v>2106.518375971927</v>
+        <v>2278.742158480318</v>
       </c>
       <c r="C237" t="n">
-        <v>1863.557074373288</v>
+        <v>2040.53277138776</v>
       </c>
       <c r="D237" t="n">
-        <v>2372.138383860763</v>
+        <v>2525.825783091488</v>
       </c>
       <c r="E237" t="n">
-        <v>2203.671630859375</v>
+        <v>2359.43701171875</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46100</v>
+        <v>46128</v>
       </c>
       <c r="B238" t="n">
-        <v>2063.293746748941</v>
+        <v>2250.444438607995</v>
       </c>
       <c r="C238" t="n">
-        <v>1810.223740874677</v>
+        <v>1995.118958214893</v>
       </c>
       <c r="D238" t="n">
-        <v>2343.06930207998</v>
+        <v>2497.722051999613</v>
       </c>
       <c r="E238" t="n">
-        <v>2137.423828125</v>
+        <v>2348.64501953125</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46101</v>
+        <v>46129</v>
       </c>
       <c r="B239" t="n">
-        <v>2068.692521119485</v>
+        <v>2260.131892946818</v>
       </c>
       <c r="C239" t="n">
-        <v>1806.594492850076</v>
+        <v>2031.054271307034</v>
       </c>
       <c r="D239" t="n">
-        <v>2322.061536452011</v>
+        <v>2519.787372824896</v>
       </c>
       <c r="E239" t="n">
-        <v>2146.4970703125</v>
+        <v>2421.07177734375</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46102</v>
+        <v>46130</v>
       </c>
       <c r="B240" t="n">
-        <v>2076.974221358322</v>
+        <v>2271.112647559642</v>
       </c>
       <c r="C240" t="n">
-        <v>1819.231641341934</v>
+        <v>2026.838229221347</v>
       </c>
       <c r="D240" t="n">
-        <v>2346.798795993711</v>
+        <v>2533.87438009414</v>
       </c>
       <c r="E240" t="n">
-        <v>2076.68994140625</v>
+        <v>2351.1005859375</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46103</v>
+        <v>46131</v>
       </c>
       <c r="B241" t="n">
-        <v>2100.047521641768</v>
+        <v>2302.677977652735</v>
       </c>
       <c r="C241" t="n">
-        <v>1843.48232356783</v>
+        <v>2082.109702358839</v>
       </c>
       <c r="D241" t="n">
-        <v>2360.378118891777</v>
+        <v>2545.443954587657</v>
       </c>
       <c r="E241" t="n">
-        <v>2053.04833984375</v>
+        <v>2264.9169921875</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46104</v>
+        <v>46132</v>
       </c>
       <c r="B242" t="n">
-        <v>2103.473054972583</v>
+        <v>2309.137736005935</v>
       </c>
       <c r="C242" t="n">
-        <v>1845.296264431581</v>
+        <v>2086.486428489471</v>
       </c>
       <c r="D242" t="n">
-        <v>2380.174445740333</v>
+        <v>2553.369657734932</v>
       </c>
       <c r="E242" t="n">
-        <v>2152.14599609375</v>
+        <v>2315.21240234375</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46105</v>
+        <v>46133</v>
       </c>
       <c r="B243" t="n">
-        <v>2097.916949130415</v>
+        <v>2311.01775288874</v>
       </c>
       <c r="C243" t="n">
-        <v>1844.71360769525</v>
+        <v>2080.748585046167</v>
       </c>
       <c r="D243" t="n">
-        <v>2378.17009663158</v>
+        <v>2549.020003361301</v>
       </c>
       <c r="E243" t="n">
-        <v>2155.704345703125</v>
+        <v>2327.970458984375</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46106</v>
+        <v>46134</v>
       </c>
       <c r="B244" t="n">
-        <v>2118.308624338239</v>
+        <v>2334.527348564382</v>
       </c>
       <c r="C244" t="n">
-        <v>1835.555536233225</v>
+        <v>2091.229845212641</v>
       </c>
       <c r="D244" t="n">
-        <v>2373.378246999965</v>
+        <v>2573.493431178968</v>
       </c>
       <c r="E244" t="n">
-        <v>2168.021484375</v>
+        <v>2376.088134765625</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46107</v>
+        <v>46135</v>
       </c>
       <c r="B245" t="n">
-        <v>2078.536539173793</v>
+        <v>2305.491443469904</v>
       </c>
       <c r="C245" t="n">
-        <v>1809.070955655072</v>
+        <v>2088.713585413694</v>
       </c>
       <c r="D245" t="n">
-        <v>2323.751069813907</v>
+        <v>2541.997307406507</v>
       </c>
       <c r="E245" t="n">
-        <v>2059.578369140625</v>
+        <v>2331.513916015625</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46108</v>
+        <v>46136</v>
       </c>
       <c r="B246" t="n">
-        <v>2087.557656584172</v>
+        <v>2314.060912789168</v>
       </c>
       <c r="C246" t="n">
-        <v>1820.46357532818</v>
+        <v>2067.153620874351</v>
       </c>
       <c r="D246" t="n">
-        <v>2358.65879868337</v>
+        <v>2548.242291369027</v>
       </c>
       <c r="E246" t="n">
-        <v>1991.27197265625</v>
+        <v>2315.690185546875</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46109</v>
+        <v>46137</v>
       </c>
       <c r="B247" t="n">
-        <v>2099.552744772527</v>
+        <v>2323.452702818348</v>
       </c>
       <c r="C247" t="n">
-        <v>1837.119369739617</v>
+        <v>2091.952463891622</v>
       </c>
       <c r="D247" t="n">
-        <v>2365.666860080564</v>
+        <v>2557.744706632212</v>
       </c>
       <c r="E247" t="n">
-        <v>1992.694580078125</v>
+        <v>2318.8291015625</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46110</v>
+        <v>46138</v>
       </c>
       <c r="B248" t="n">
-        <v>2126.362092511747</v>
+        <v>2352.871108068875</v>
       </c>
       <c r="C248" t="n">
-        <v>1877.287781268136</v>
+        <v>2123.615982225223</v>
       </c>
       <c r="D248" t="n">
-        <v>2381.456701091685</v>
+        <v>2584.454768478402</v>
       </c>
       <c r="E248" t="n">
-        <v>1982.559692382812</v>
+        <v>2369.72900390625</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="B249" t="n">
-        <v>2133.489235985343</v>
+        <v>2356.546875048574</v>
       </c>
       <c r="C249" t="n">
-        <v>1862.737209584503</v>
+        <v>2126.011444749459</v>
       </c>
       <c r="D249" t="n">
-        <v>2400.033716449905</v>
+        <v>2621.944066029243</v>
       </c>
       <c r="E249" t="n">
-        <v>2023.514892578125</v>
+        <v>2303.06396484375</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46112</v>
+        <v>46140</v>
       </c>
       <c r="B250" t="n">
-        <v>2131.554804048531</v>
+        <v>2354.938061248514</v>
       </c>
       <c r="C250" t="n">
-        <v>1865.02388233716</v>
+        <v>2118.981341451722</v>
       </c>
       <c r="D250" t="n">
-        <v>2398.599535472261</v>
+        <v>2601.644134267657</v>
       </c>
       <c r="E250" t="n">
-        <v>2104.708251953125</v>
+        <v>2289.419677734375</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46113</v>
+        <v>46141</v>
       </c>
       <c r="B251" t="n">
-        <v>2155.454047652612</v>
+        <v>2374.200665429907</v>
       </c>
       <c r="C251" t="n">
-        <v>1885.771928181833</v>
+        <v>2137.004802651152</v>
       </c>
       <c r="D251" t="n">
-        <v>2415.258722965285</v>
+        <v>2601.965493974751</v>
       </c>
       <c r="E251" t="n">
-        <v>2138.737060546875</v>
+        <v>2253.415771484375</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46114</v>
+        <v>46142</v>
       </c>
       <c r="B252" t="n">
-        <v>2119.051792828005</v>
+        <v>2340.123401323002</v>
       </c>
       <c r="C252" t="n">
-        <v>1848.744350480587</v>
+        <v>2083.826082808145</v>
       </c>
       <c r="D252" t="n">
-        <v>2380.054855587225</v>
+        <v>2576.627954608406</v>
       </c>
       <c r="E252" t="n">
-        <v>2056.8525390625</v>
+        <v>2256.251220703125</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
-        <v>46115</v>
+        <v>46143</v>
       </c>
       <c r="B253" t="n">
-        <v>2131.290659578638</v>
+        <v>2342.840164515042</v>
       </c>
       <c r="C253" t="n">
-        <v>1853.128319700893</v>
+        <v>2083.559203043828</v>
       </c>
       <c r="D253" t="n">
-        <v>2394.289788480407</v>
+        <v>2581.404621186282</v>
       </c>
       <c r="E253" t="n">
-        <v>2053.38525390625</v>
+        <v>2295.09375</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
-        <v>46116</v>
+        <v>46144</v>
       </c>
       <c r="B254" t="n">
-        <v>2146.34474626171</v>
+        <v>2345.571632192595</v>
       </c>
       <c r="C254" t="n">
-        <v>1887.13442779516</v>
+        <v>2114.272819643248</v>
       </c>
       <c r="D254" t="n">
-        <v>2419.669170184276</v>
+        <v>2587.967818898375</v>
       </c>
       <c r="E254" t="n">
-        <v>2065.3515625</v>
+        <v>2316.23193359375</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
-        <v>46117</v>
+        <v>46145</v>
       </c>
       <c r="B255" t="n">
-        <v>2176.053455012071</v>
+        <v>2367.54733894423</v>
       </c>
       <c r="C255" t="n">
-        <v>1904.657597227867</v>
+        <v>2136.425699699648</v>
       </c>
       <c r="D255" t="n">
-        <v>2438.635992694728</v>
+        <v>2601.2970588504</v>
       </c>
       <c r="E255" t="n">
-        <v>2108.99560546875</v>
+        <v>2321.6357421875</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
-        <v>46118</v>
+        <v>46146</v>
       </c>
       <c r="B256" t="n">
-        <v>2185.923157102844</v>
+        <v>2363.044861979193</v>
       </c>
       <c r="C256" t="n">
-        <v>1928.280730403791</v>
+        <v>2143.604918878111</v>
       </c>
       <c r="D256" t="n">
-        <v>2441.421489010173</v>
+        <v>2596.91025651573</v>
       </c>
       <c r="E256" t="n">
-        <v>2107.761474609375</v>
+        <v>2346.39697265625</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
-        <v>46119</v>
+        <v>46147</v>
       </c>
       <c r="B257" t="n">
-        <v>2186.578911246952</v>
+        <v>2352.590037011241</v>
       </c>
       <c r="C257" t="n">
-        <v>1918.449733893727</v>
+        <v>2125.719156180784</v>
       </c>
       <c r="D257" t="n">
-        <v>2452.674713296837</v>
+        <v>2606.428516056605</v>
       </c>
       <c r="E257" t="n">
-        <v>2241.806640625</v>
+        <v>2361.1826171875</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
-        <v>46120</v>
+        <v>46148</v>
       </c>
       <c r="B258" t="n">
-        <v>2212.919904443784</v>
+        <v>2362.426238013841</v>
       </c>
       <c r="C258" t="n">
-        <v>1954.895466783643</v>
+        <v>2123.90179443989</v>
       </c>
       <c r="D258" t="n">
-        <v>2481.624578076581</v>
+        <v>2601.316337836298</v>
       </c>
       <c r="E258" t="n">
-        <v>2190.33544921875</v>
+        <v>2350.802001953125</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
-        <v>46121</v>
+        <v>46149</v>
       </c>
       <c r="B259" t="n">
-        <v>2178.812453922211</v>
+        <v>2318.447134684615</v>
       </c>
       <c r="C259" t="n">
-        <v>1920.953790947991</v>
+        <v>2079.849736069853</v>
       </c>
       <c r="D259" t="n">
-        <v>2462.67665937385</v>
+        <v>2553.346209675376</v>
       </c>
       <c r="E259" t="n">
-        <v>2189.14404296875</v>
+        <v>2291.107666015625</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
-        <v>46122</v>
+        <v>46150</v>
       </c>
       <c r="B260" t="n">
-        <v>2193.196503431846</v>
+        <v>2310.906540865287</v>
       </c>
       <c r="C260" t="n">
-        <v>1942.973703263906</v>
+        <v>2076.909559150364</v>
       </c>
       <c r="D260" t="n">
-        <v>2434.185778556121</v>
+        <v>2546.639507733055</v>
       </c>
       <c r="E260" t="n">
-        <v>2245.148681640625</v>
+        <v>2306.97216796875</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
-        <v>46123</v>
+        <v>46151</v>
       </c>
       <c r="B261" t="n">
-        <v>2210.237891293793</v>
+        <v>2303.15688028364</v>
       </c>
       <c r="C261" t="n">
-        <v>1937.448680643507</v>
+        <v>2079.357797844251</v>
       </c>
       <c r="D261" t="n">
-        <v>2472.83876273465</v>
+        <v>2553.658513407019</v>
       </c>
       <c r="E261" t="n">
-        <v>2285.39013671875</v>
+        <v>2326.727294921875</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
-        <v>46124</v>
+        <v>46152</v>
       </c>
       <c r="B262" t="n">
-        <v>2241.76113052483</v>
+        <v>2314.567713819647</v>
       </c>
       <c r="C262" t="n">
-        <v>1968.969092741967</v>
+        <v>2088.053783110412</v>
       </c>
       <c r="D262" t="n">
-        <v>2498.701835984979</v>
+        <v>2541.511651158227</v>
       </c>
       <c r="E262" t="n">
-        <v>2192.201171875</v>
+        <v>2369.0439453125</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
-        <v>46125</v>
+        <v>46153</v>
       </c>
       <c r="B263" t="n">
-        <v>2253.250446741786</v>
+        <v>2299.561079550053</v>
       </c>
       <c r="C263" t="n">
-        <v>1986.519215486003</v>
+        <v>2056.397392347636</v>
       </c>
       <c r="D263" t="n">
-        <v>2522.477657543835</v>
+        <v>2555.420746400218</v>
       </c>
       <c r="E263" t="n">
-        <v>2370.71484375</v>
+        <v>2339.36083984375</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
-        <v>46126</v>
+        <v>46154</v>
       </c>
       <c r="B264" t="n">
-        <v>2255.301315833329</v>
+        <v>2278.807694051187</v>
       </c>
       <c r="C264" t="n">
-        <v>2017.708062821878</v>
+        <v>2027.614145937291</v>
       </c>
       <c r="D264" t="n">
-        <v>2517.188429187762</v>
+        <v>2519.950456332056</v>
       </c>
       <c r="E264" t="n">
-        <v>2323.30859375</v>
+        <v>2274.6435546875</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>46127</v>
+        <v>46155</v>
       </c>
       <c r="B265" t="n">
-        <v>2282.776180791697</v>
+        <v>2278.692181677561</v>
       </c>
       <c r="C265" t="n">
-        <v>2014.674751819616</v>
+        <v>2050.281462137686</v>
       </c>
       <c r="D265" t="n">
-        <v>2535.844034362736</v>
+        <v>2532.960441426528</v>
       </c>
       <c r="E265" t="n">
-        <v>2359.43701171875</v>
+        <v>2257.576416015625</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
-        <v>46128</v>
+        <v>46156</v>
       </c>
       <c r="B266" t="n">
-        <v>2249.498176897242</v>
+        <v>2225.241880607412</v>
       </c>
       <c r="C266" t="n">
-        <v>1996.286668320086</v>
+        <v>1992.339130167971</v>
       </c>
       <c r="D266" t="n">
-        <v>2523.683603052116</v>
+        <v>2469.794868480687</v>
       </c>
       <c r="E266" t="n">
-        <v>2348.64501953125</v>
+        <v>2280.934814453125</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>46129</v>
+        <v>46157</v>
       </c>
       <c r="B267" t="n">
-        <v>2264.358770043686</v>
+        <v>2208.832971993347</v>
       </c>
       <c r="C267" t="n">
-        <v>2011.087447243466</v>
+        <v>1974.037561825829</v>
       </c>
       <c r="D267" t="n">
-        <v>2521.395401051626</v>
+        <v>2454.185246655275</v>
       </c>
       <c r="E267" t="n">
-        <v>2421.07177734375</v>
+        <v>2223.328857421875</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>46130</v>
+        <v>46158</v>
       </c>
       <c r="B268" t="n">
-        <v>2281.471540930948</v>
+        <v>2192.925581724011</v>
       </c>
       <c r="C268" t="n">
-        <v>2032.114736257431</v>
+        <v>1948.838432189089</v>
       </c>
       <c r="D268" t="n">
-        <v>2562.441405642986</v>
+        <v>2428.487325318855</v>
       </c>
       <c r="E268" t="n">
-        <v>2351.1005859375</v>
+        <v>2179.751953125</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>46131</v>
+        <v>46159</v>
       </c>
       <c r="B269" t="n">
-        <v>2312.606793729816</v>
+        <v>2196.979414052892</v>
       </c>
       <c r="C269" t="n">
-        <v>2054.507640001227</v>
+        <v>1957.88795223925</v>
       </c>
       <c r="D269" t="n">
-        <v>2595.482494614415</v>
+        <v>2432.636074686269</v>
       </c>
       <c r="E269" t="n">
-        <v>2264.9169921875</v>
+        <v>2127.645263671875</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>46132</v>
+        <v>46160</v>
       </c>
       <c r="B270" t="n">
-        <v>2323.194661314732</v>
+        <v>2175.486765415105</v>
       </c>
       <c r="C270" t="n">
-        <v>2059.48490214543</v>
+        <v>1928.523233555217</v>
       </c>
       <c r="D270" t="n">
-        <v>2589.656424109807</v>
+        <v>2424.492337744323</v>
       </c>
       <c r="E270" t="n">
-        <v>2315.21240234375</v>
+        <v>2128.51611328125</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>46133</v>
+        <v>46161</v>
       </c>
       <c r="B271" t="n">
-        <v>2323.778864935586</v>
+        <v>2149.167046307065</v>
       </c>
       <c r="C271" t="n">
-        <v>2057.355086325858</v>
+        <v>1915.647585961912</v>
       </c>
       <c r="D271" t="n">
-        <v>2585.372117897268</v>
+        <v>2398.830905248401</v>
       </c>
       <c r="E271" t="n">
-        <v>2327.970458984375</v>
+        <v>2109.9638671875</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>46134</v>
+        <v>46162</v>
       </c>
       <c r="B272" t="n">
-        <v>2349.174716113483</v>
+        <v>2144.431035788808</v>
       </c>
       <c r="C272" t="n">
-        <v>2098.578978652522</v>
+        <v>1898.440618959988</v>
       </c>
       <c r="D272" t="n">
-        <v>2625.006551387203</v>
+        <v>2378.460962703734</v>
       </c>
       <c r="E272" t="n">
-        <v>2376.088134765625</v>
+        <v>2126.9833984375</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>46135</v>
+        <v>46163</v>
       </c>
       <c r="B273" t="n">
-        <v>2313.165096586788</v>
+        <v>2087.309451644266</v>
       </c>
       <c r="C273" t="n">
-        <v>2046.819596921588</v>
+        <v>1859.638563575494</v>
       </c>
       <c r="D273" t="n">
-        <v>2584.365963709527</v>
+        <v>2335.613523933494</v>
       </c>
       <c r="E273" t="n">
-        <v>2331.513916015625</v>
+        <v>2131.41064453125</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>46136</v>
+        <v>46164</v>
       </c>
       <c r="B274" t="n">
-        <v>2324.610225702582</v>
+        <v>2068.159592284838</v>
       </c>
       <c r="C274" t="n">
-        <v>2078.235776537491</v>
+        <v>1825.699942741018</v>
       </c>
       <c r="D274" t="n">
-        <v>2604.137949220627</v>
+        <v>2311.564067146911</v>
       </c>
       <c r="E274" t="n">
-        <v>2315.690185546875</v>
+        <v>2064.636962890625</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>46137</v>
+        <v>46165</v>
       </c>
       <c r="B275" t="n">
-        <v>2337.603358018532</v>
+        <v>2050.401684350502</v>
       </c>
       <c r="C275" t="n">
-        <v>2092.538726924518</v>
+        <v>1815.302197245193</v>
       </c>
       <c r="D275" t="n">
-        <v>2626.897446746023</v>
+        <v>2287.093433647561</v>
       </c>
       <c r="E275" t="n">
-        <v>2318.8291015625</v>
+        <v>2115.951416015625</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>46138</v>
+        <v>46166</v>
       </c>
       <c r="B276" t="n">
-        <v>2363.907006309257</v>
+        <v>2053.436455008897</v>
       </c>
       <c r="C276" t="n">
-        <v>2101.183546683398</v>
+        <v>1820.568421438759</v>
       </c>
       <c r="D276" t="n">
-        <v>2607.351487580132</v>
+        <v>2289.060493602528</v>
       </c>
       <c r="E276" t="n">
-        <v>2369.72900390625</v>
+        <v>2097.993896484375</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>46139</v>
+        <v>46167</v>
       </c>
       <c r="B277" t="n">
-        <v>2368.957289174594</v>
+        <v>2031.680713460452</v>
       </c>
       <c r="C277" t="n">
-        <v>2108.923085083669</v>
+        <v>1810.145575826854</v>
       </c>
       <c r="D277" t="n">
-        <v>2629.911961503492</v>
+        <v>2264.234825947725</v>
       </c>
       <c r="E277" t="n">
-        <v>2303.06396484375</v>
+        <v>2111.370361328125</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>46140</v>
+        <v>46168</v>
       </c>
       <c r="B278" t="n">
-        <v>2363.318501322922</v>
+        <v>2005.764984131444</v>
       </c>
       <c r="C278" t="n">
-        <v>2114.542574867191</v>
+        <v>1779.895778697764</v>
       </c>
       <c r="D278" t="n">
-        <v>2623.661170675462</v>
+        <v>2235.552447906372</v>
       </c>
       <c r="E278" t="n">
-        <v>2289.419677734375</v>
+        <v>2070.858154296875</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>46141</v>
+        <v>46169</v>
       </c>
       <c r="B279" t="n">
-        <v>2381.841450720469</v>
+        <v>2002.001311795099</v>
       </c>
       <c r="C279" t="n">
-        <v>2096.59596691177</v>
+        <v>1761.405278815608</v>
       </c>
       <c r="D279" t="n">
-        <v>2625.269127204013</v>
+        <v>2225.193025669054</v>
       </c>
       <c r="E279" t="n">
-        <v>2253.415771484375</v>
+        <v>2022.1982421875</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>46142</v>
+        <v>46170</v>
       </c>
       <c r="B280" t="n">
-        <v>2338.359270513063</v>
+        <v>1946.315701954964</v>
       </c>
       <c r="C280" t="n">
-        <v>2087.128261660951</v>
+        <v>1706.745089999403</v>
       </c>
       <c r="D280" t="n">
-        <v>2599.337421788318</v>
+        <v>2197.392852028383</v>
       </c>
       <c r="E280" t="n">
-        <v>2256.251220703125</v>
+        <v>2007.552734375</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>46143</v>
+        <v>46171</v>
       </c>
       <c r="B281" t="n">
-        <v>2341.796507890136</v>
+        <v>1928.958820994578</v>
       </c>
       <c r="C281" t="n">
-        <v>2073.793473558441</v>
+        <v>1694.865594556398</v>
       </c>
       <c r="D281" t="n">
-        <v>2618.237301363553</v>
+        <v>2178.023203795903</v>
       </c>
       <c r="E281" t="n">
-        <v>2295.09375</v>
+        <v>2011.978515625</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>46144</v>
+        <v>46172</v>
       </c>
       <c r="B282" t="n">
-        <v>2346.323642807793</v>
+        <v>1913.246451291076</v>
       </c>
       <c r="C282" t="n">
-        <v>2097.015424230073</v>
+        <v>1662.891793873725</v>
       </c>
       <c r="D282" t="n">
-        <v>2605.315799798527</v>
+        <v>2149.244434394137</v>
       </c>
       <c r="E282" t="n">
-        <v>2316.23193359375</v>
+        <v>2019.458251953125</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>46145</v>
+        <v>46173</v>
       </c>
       <c r="B283" t="n">
-        <v>2363.79166112416</v>
+        <v>1918.481078292571</v>
       </c>
       <c r="C283" t="n">
-        <v>2108.937336653437</v>
+        <v>1667.68451298026</v>
       </c>
       <c r="D283" t="n">
-        <v>2641.977391519697</v>
+        <v>2152.0618860932</v>
       </c>
       <c r="E283" t="n">
-        <v>2321.6357421875</v>
+        <v>2004.341552734375</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>46146</v>
+        <v>46174</v>
       </c>
       <c r="B284" t="n">
-        <v>2359.734329209522</v>
+        <v>1898.99125474478</v>
       </c>
       <c r="C284" t="n">
-        <v>2097.771479222662</v>
+        <v>1678.685009681504</v>
       </c>
       <c r="D284" t="n">
-        <v>2622.511319648082</v>
+        <v>2128.587401571683</v>
       </c>
       <c r="E284" t="n">
-        <v>2346.39697265625</v>
+        <v>2003.22119140625</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>46147</v>
+        <v>46175</v>
       </c>
       <c r="B285" t="n">
-        <v>2344.820331534973</v>
+        <v>1875.332650587144</v>
       </c>
       <c r="C285" t="n">
-        <v>2066.000540657802</v>
+        <v>1640.132624136907</v>
       </c>
       <c r="D285" t="n">
-        <v>2596.566405601155</v>
+        <v>2118.935261340881</v>
       </c>
       <c r="E285" t="n">
-        <v>2361.1826171875</v>
+        <v>1857.71630859375</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>46148</v>
+        <v>46176</v>
       </c>
       <c r="B286" t="n">
-        <v>2354.008893864589</v>
+        <v>1873.758786593671</v>
       </c>
       <c r="C286" t="n">
-        <v>2084.471386144744</v>
+        <v>1631.969535808298</v>
       </c>
       <c r="D286" t="n">
-        <v>2618.055192705385</v>
+        <v>2105.323854204674</v>
       </c>
       <c r="E286" t="n">
-        <v>2350.802001953125</v>
+        <v>1811.732299804688</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>46149</v>
+        <v>46177</v>
       </c>
       <c r="B287" t="n">
-        <v>2301.242689833743</v>
+        <v>1820.155807696516</v>
       </c>
       <c r="C287" t="n">
-        <v>2039.280391629569</v>
+        <v>1585.104665548981</v>
       </c>
       <c r="D287" t="n">
-        <v>2562.549075788593</v>
+        <v>2057.43467483739</v>
       </c>
       <c r="E287" t="n">
-        <v>2291.107666015625</v>
+        <v>1769.58056640625</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>46150</v>
+        <v>46178</v>
       </c>
       <c r="B288" t="n">
-        <v>2295.553931625488</v>
+        <v>1804.754831980364</v>
       </c>
       <c r="C288" t="n">
-        <v>2041.036644132802</v>
+        <v>1568.729477694789</v>
       </c>
       <c r="D288" t="n">
-        <v>2549.009205146857</v>
+        <v>2048.656126775887</v>
       </c>
       <c r="E288" t="n">
-        <v>2306.97216796875</v>
+        <v>1580.86083984375</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>46151</v>
+        <v>46179</v>
       </c>
       <c r="B289" t="n">
-        <v>2291.215901373858</v>
+        <v>1790.873303897891</v>
       </c>
       <c r="C289" t="n">
-        <v>2024.886200399092</v>
+        <v>1554.293161729208</v>
       </c>
       <c r="D289" t="n">
-        <v>2559.919298134469</v>
+        <v>2024.820271450352</v>
       </c>
       <c r="E289" t="n">
-        <v>2326.727294921875</v>
+        <v>1568.767700195312</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>46152</v>
+        <v>46180</v>
       </c>
       <c r="B290" t="n">
-        <v>2300.174653387154</v>
+        <v>1797.836686784465</v>
       </c>
       <c r="C290" t="n">
-        <v>2024.622306149496</v>
+        <v>1555.055506440693</v>
       </c>
       <c r="D290" t="n">
-        <v>2568.202832398035</v>
+        <v>2047.246051139326</v>
       </c>
       <c r="E290" t="n">
-        <v>2369.0439453125</v>
+        <v>1686.396240234375</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>46153</v>
+        <v>46181</v>
       </c>
       <c r="B291" t="n">
-        <v>2288.048636967246</v>
+        <v>1780.0171231404</v>
       </c>
       <c r="C291" t="n">
-        <v>2018.576523360208</v>
+        <v>1529.425204865627</v>
       </c>
       <c r="D291" t="n">
-        <v>2565.179505428283</v>
+        <v>2004.559053816429</v>
       </c>
       <c r="E291" t="n">
-        <v>2339.36083984375</v>
+        <v>1690.148559570312</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>46154</v>
+        <v>46182</v>
       </c>
       <c r="B292" t="n">
-        <v>2265.57849903677</v>
+        <v>1758.032982518504</v>
       </c>
       <c r="C292" t="n">
-        <v>2006.160479339383</v>
+        <v>1526.340244216267</v>
       </c>
       <c r="D292" t="n">
-        <v>2522.960174241659</v>
+        <v>1996.846704295978</v>
       </c>
       <c r="E292" t="n">
-        <v>2274.6435546875</v>
+        <v>1637.706665039062</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>46155</v>
+        <v>46183</v>
       </c>
       <c r="B293" t="n">
-        <v>2267.780776826738</v>
+        <v>1758.217332455887</v>
       </c>
       <c r="C293" t="n">
-        <v>2002.803180219446</v>
+        <v>1529.530672947872</v>
       </c>
       <c r="D293" t="n">
-        <v>2546.298261143295</v>
+        <v>1990.911367002628</v>
       </c>
       <c r="E293" t="n">
-        <v>2257.576416015625</v>
+        <v>1620.1376953125</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>46156</v>
+        <v>46184</v>
       </c>
       <c r="B294" t="n">
-        <v>2208.63935353918</v>
+        <v>1706.549752052248</v>
       </c>
       <c r="C294" t="n">
-        <v>1953.512797718348</v>
+        <v>1477.212210393186</v>
       </c>
       <c r="D294" t="n">
-        <v>2470.293429810739</v>
+        <v>1953.28942359971</v>
       </c>
       <c r="E294" t="n">
-        <v>2280.934814453125</v>
+        <v>1672.280639648438</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>46157</v>
+        <v>46185</v>
       </c>
       <c r="B295" t="n">
-        <v>2197.210637525679</v>
+        <v>1693.365112465288</v>
       </c>
       <c r="C295" t="n">
-        <v>1935.604743327157</v>
+        <v>1442.08974131145</v>
       </c>
       <c r="D295" t="n">
-        <v>2482.915846558778</v>
+        <v>1909.123668682735</v>
       </c>
       <c r="E295" t="n">
-        <v>2223.328857421875</v>
+        <v>1665.127807617188</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>46158</v>
+        <v>46186</v>
       </c>
       <c r="B296" t="n">
-        <v>2187.774762736472</v>
+        <v>1682.090861971761</v>
       </c>
       <c r="C296" t="n">
-        <v>1925.974198677913</v>
+        <v>1445.450958699389</v>
       </c>
       <c r="D296" t="n">
-        <v>2438.219165996979</v>
+        <v>1937.163843148596</v>
       </c>
       <c r="E296" t="n">
-        <v>2179.751953125</v>
+        <v>1680.214599609375</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>46159</v>
+        <v>46187</v>
       </c>
       <c r="B297" t="n">
-        <v>2192.26756294651</v>
+        <v>1692.164279578371</v>
       </c>
       <c r="C297" t="n">
-        <v>1934.686998385314</v>
+        <v>1433.487019278033</v>
       </c>
       <c r="D297" t="n">
-        <v>2456.962333655781</v>
+        <v>1918.198617137425</v>
       </c>
       <c r="E297" t="n">
-        <v>2127.645263671875</v>
+        <v>1724.61328125</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>46160</v>
+        <v>46188</v>
       </c>
       <c r="B298" t="n">
-        <v>2176.281070329548</v>
+        <v>1678.066468239204</v>
       </c>
       <c r="C298" t="n">
-        <v>1929.657315830083</v>
+        <v>1439.75221490876</v>
       </c>
       <c r="D298" t="n">
-        <v>2430.608462282207</v>
+        <v>1922.110503766945</v>
       </c>
       <c r="E298" t="n">
-        <v>2128.51611328125</v>
+        <v>1794.961181640625</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>46161</v>
+        <v>46189</v>
       </c>
       <c r="B299" t="n">
-        <v>2150.514777421399</v>
+        <v>1660.517160735962</v>
       </c>
       <c r="C299" t="n">
-        <v>1894.346916953181</v>
+        <v>1428.592792415012</v>
       </c>
       <c r="D299" t="n">
-        <v>2426.70731271474</v>
+        <v>1902.598194004417</v>
       </c>
       <c r="E299" t="n">
-        <v>2109.9638671875</v>
+        <v>1790.398193359375</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>46162</v>
+        <v>46190</v>
       </c>
       <c r="B300" t="n">
-        <v>2149.931331509411</v>
+        <v>1665.938532295632</v>
       </c>
       <c r="C300" t="n">
-        <v>1890.568924657466</v>
+        <v>1441.245670686096</v>
       </c>
       <c r="D300" t="n">
-        <v>2397.862318403692</v>
+        <v>1910.760097091194</v>
       </c>
       <c r="E300" t="n">
-        <v>2126.9833984375</v>
+        <v>1747.885498046875</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>46163</v>
+        <v>46191</v>
       </c>
       <c r="B301" t="n">
-        <v>2088.450473252962</v>
+        <v>1620.382598705232</v>
       </c>
       <c r="C301" t="n">
-        <v>1831.052384520406</v>
+        <v>1377.393052511205</v>
       </c>
       <c r="D301" t="n">
-        <v>2342.842921007466</v>
+        <v>1857.13970790029</v>
       </c>
       <c r="E301" t="n">
-        <v>2131.41064453125</v>
+        <v>1709.533447265625</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
-        <v>46164</v>
+        <v>46192</v>
       </c>
       <c r="B302" t="n">
-        <v>2075.057100428747</v>
+        <v>1614.235978343804</v>
       </c>
       <c r="C302" t="n">
-        <v>1790.000639472235</v>
+        <v>1374.775046685323</v>
       </c>
       <c r="D302" t="n">
-        <v>2348.01391251568</v>
+        <v>1845.412191428165</v>
       </c>
       <c r="E302" t="n">
-        <v>2064.636962890625</v>
+        <v>1710.982421875</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>46165</v>
+        <v>46193</v>
       </c>
       <c r="B303" t="n">
-        <v>2063.955659821102</v>
+        <v>1610.953701262511</v>
       </c>
       <c r="C303" t="n">
-        <v>1809.617298701326</v>
+        <v>1386.938339350469</v>
       </c>
       <c r="D303" t="n">
-        <v>2332.712907506798</v>
+        <v>1832.376024826815</v>
       </c>
       <c r="E303" t="n">
-        <v>2115.951416015625</v>
+        <v>1739.301391601562</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
-        <v>46166</v>
+        <v>46194</v>
       </c>
       <c r="B304" t="n">
-        <v>2067.00551112701</v>
+        <v>1629.973659088664</v>
       </c>
       <c r="C304" t="n">
-        <v>1783.632890583993</v>
+        <v>1374.852507669942</v>
       </c>
       <c r="D304" t="n">
-        <v>2321.662921798558</v>
+        <v>1866.847706789952</v>
       </c>
       <c r="E304" t="n">
-        <v>2097.993896484375</v>
+        <v>1704.58056640625</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
-        <v>46167</v>
+        <v>46195</v>
       </c>
       <c r="B305" t="n">
-        <v>2049.724896152129</v>
+        <v>1625.748578782609</v>
       </c>
       <c r="C305" t="n">
-        <v>1768.105950844689</v>
+        <v>1372.113248134043</v>
       </c>
       <c r="D305" t="n">
-        <v>2305.709411101845</v>
+        <v>1858.075167854894</v>
       </c>
       <c r="E305" t="n">
-        <v>2111.370361328125</v>
+        <v>1726.510864257812</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
-        <v>46168</v>
+        <v>46196</v>
       </c>
       <c r="B306" t="n">
-        <v>2022.74562913369</v>
+        <v>1618.939682260905</v>
       </c>
       <c r="C306" t="n">
-        <v>1771.480186458047</v>
+        <v>1372.141424047822</v>
       </c>
       <c r="D306" t="n">
-        <v>2281.145736881062</v>
+        <v>1841.793658836877</v>
       </c>
       <c r="E306" t="n">
-        <v>2070.858154296875</v>
+        <v>1665.436767578125</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
-        <v>46169</v>
+        <v>46197</v>
       </c>
       <c r="B307" t="n">
-        <v>2020.97205259809</v>
+        <v>1635.880289150162</v>
       </c>
       <c r="C307" t="n">
-        <v>1774.098815077846</v>
+        <v>1385.446267716413</v>
       </c>
       <c r="D307" t="n">
-        <v>2273.037191851582</v>
+        <v>1870.246763585189</v>
       </c>
       <c r="E307" t="n">
-        <v>2022.1982421875</v>
+        <v>1619.924926757812</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
-        <v>46170</v>
+        <v>46198</v>
       </c>
       <c r="B308" t="n">
-        <v>1958.277948665351</v>
+        <v>1602.503976372015</v>
       </c>
       <c r="C308" t="n">
-        <v>1680.458153474547</v>
+        <v>1373.243567524619</v>
       </c>
       <c r="D308" t="n">
-        <v>2233.387689634355</v>
+        <v>1836.416457672386</v>
       </c>
       <c r="E308" t="n">
-        <v>2007.552734375</v>
+        <v>1564.816650390625</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
-        <v>46171</v>
+        <v>46199</v>
       </c>
       <c r="B309" t="n">
-        <v>1943.617171768023</v>
+        <v>1609.051078078301</v>
       </c>
       <c r="C309" t="n">
-        <v>1684.392931365745</v>
+        <v>1389.806161366285</v>
       </c>
       <c r="D309" t="n">
-        <v>2202.078134373718</v>
+        <v>1848.997728382748</v>
       </c>
       <c r="E309" t="n">
-        <v>2011.978515625</v>
+        <v>1576.616088867188</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
-        <v>46172</v>
+        <v>46200</v>
       </c>
       <c r="B310" t="n">
-        <v>1931.18010191772</v>
+        <v>1618.805183655362</v>
       </c>
       <c r="C310" t="n">
-        <v>1674.682900134479</v>
+        <v>1372.131949506619</v>
       </c>
       <c r="D310" t="n">
-        <v>2188.331029899181</v>
+        <v>1856.909824705284</v>
       </c>
       <c r="E310" t="n">
-        <v>2019.458251953125</v>
+        <v>1571.588256835938</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
-        <v>46173</v>
+        <v>46201</v>
       </c>
       <c r="B311" t="n">
-        <v>1932.830473328954</v>
+        <v>1651.011171904199</v>
       </c>
       <c r="C311" t="n">
-        <v>1661.695828693069</v>
+        <v>1412.218056427023</v>
       </c>
       <c r="D311" t="n">
-        <v>2177.410969332041</v>
+        <v>1914.732084749918</v>
       </c>
       <c r="E311" t="n">
-        <v>2004.341552734375</v>
+        <v>1570.361206054688</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
-        <v>46174</v>
+        <v>46202</v>
       </c>
       <c r="B312" t="n">
-        <v>1914.110140805004</v>
+        <v>1659.911579705708</v>
       </c>
       <c r="C312" t="n">
-        <v>1648.71158843341</v>
+        <v>1431.539618775724</v>
       </c>
       <c r="D312" t="n">
-        <v>2172.919672462733</v>
+        <v>1906.576146657459</v>
       </c>
       <c r="E312" t="n">
-        <v>2003.22119140625</v>
+        <v>1610.205810546875</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
-        <v>46175</v>
+        <v>46203</v>
       </c>
       <c r="B313" t="n">
-        <v>1885.693849886681</v>
+        <v>1665.945355518968</v>
       </c>
       <c r="C313" t="n">
-        <v>1625.402777307203</v>
+        <v>1432.880073982377</v>
       </c>
       <c r="D313" t="n">
-        <v>2160.298177228639</v>
+        <v>1917.191720170776</v>
       </c>
       <c r="E313" t="n">
-        <v>1857.71630859375</v>
+        <v>1569.583862304688</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
-        <v>46176</v>
+        <v>46204</v>
       </c>
       <c r="B314" t="n">
-        <v>1882.547528559697</v>
+        <v>1695.217119342764</v>
       </c>
       <c r="C314" t="n">
-        <v>1619.542599318991</v>
+        <v>1425.187557972467</v>
       </c>
       <c r="D314" t="n">
-        <v>2142.12893825342</v>
+        <v>1923.249867395275</v>
       </c>
       <c r="E314" t="n">
-        <v>1811.732299804688</v>
+        <v>1608.960693359375</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
-        <v>46177</v>
+        <v>46205</v>
       </c>
       <c r="B315" t="n">
-        <v>1818.623788516683</v>
+        <v>1673.431386980802</v>
       </c>
       <c r="C315" t="n">
-        <v>1575.072909573849</v>
+        <v>1438.439555307662</v>
       </c>
       <c r="D315" t="n">
-        <v>2083.993590960106</v>
+        <v>1924.395691856843</v>
       </c>
       <c r="E315" t="n">
-        <v>1769.58056640625</v>
+        <v>1698.16943359375</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="n">
-        <v>46178</v>
+        <v>46206</v>
       </c>
       <c r="B316" t="n">
-        <v>1802.970425428695</v>
+        <v>1690.605370465455</v>
       </c>
       <c r="C316" t="n">
-        <v>1539.744419147069</v>
+        <v>1450.769209523962</v>
       </c>
       <c r="D316" t="n">
-        <v>2073.646208353162</v>
+        <v>1932.894711551255</v>
       </c>
       <c r="E316" t="n">
-        <v>1580.86083984375</v>
+        <v>1756.518676757812</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
-        <v>46179</v>
+        <v>46207</v>
       </c>
       <c r="B317" t="n">
-        <v>1789.884066097992</v>
+        <v>1709.811829846805</v>
       </c>
       <c r="C317" t="n">
-        <v>1531.310816013351</v>
+        <v>1476.009118218198</v>
       </c>
       <c r="D317" t="n">
-        <v>2046.546343143749</v>
+        <v>1955.54247261043</v>
       </c>
       <c r="E317" t="n">
-        <v>1568.767700195312</v>
+        <v>1779.032958984375</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
-        <v>46180</v>
+        <v>46208</v>
       </c>
       <c r="B318" t="n">
-        <v>1791.343590354611</v>
+        <v>1750.103326463854</v>
       </c>
       <c r="C318" t="n">
-        <v>1548.844719786534</v>
+        <v>1527.926831802364</v>
       </c>
       <c r="D318" t="n">
-        <v>2070.23309546813</v>
+        <v>2011.78447482295</v>
       </c>
       <c r="E318" t="n">
-        <v>1686.396240234375</v>
+        <v>1783.005981445312</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
-        <v>46181</v>
+        <v>46209</v>
       </c>
       <c r="B319" t="n">
-        <v>1773.010985670859</v>
+        <v>1765.55448812231</v>
       </c>
       <c r="C319" t="n">
-        <v>1512.098129237415</v>
+        <v>1530.332338970075</v>
       </c>
       <c r="D319" t="n">
-        <v>2037.627598515451</v>
+        <v>2027.211517239061</v>
       </c>
       <c r="E319" t="n">
-        <v>1690.148559570312</v>
+        <v>1797.57373046875</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
-        <v>46182</v>
+        <v>46210</v>
       </c>
       <c r="B320" t="n">
-        <v>1745.68181604536</v>
+        <v>1776.466154435858</v>
       </c>
       <c r="C320" t="n">
-        <v>1491.100654692652</v>
+        <v>1552.833244046443</v>
       </c>
       <c r="D320" t="n">
-        <v>1986.062043659602</v>
+        <v>2018.334221082144</v>
       </c>
       <c r="E320" t="n">
-        <v>1637.706665039062</v>
+        <v>1768.511474609375</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
-        <v>46183</v>
+        <v>46211</v>
       </c>
       <c r="B321" t="n">
-        <v>1744.438955206141</v>
+        <v>1808.839353222239</v>
       </c>
       <c r="C321" t="n">
-        <v>1474.812093139737</v>
+        <v>1559.446855825074</v>
       </c>
       <c r="D321" t="n">
-        <v>2008.573873033966</v>
+        <v>2041.122721161207</v>
       </c>
       <c r="E321" t="n">
-        <v>1620.1376953125</v>
+        <v>1742.677612304688</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
-        <v>46184</v>
+        <v>46212</v>
       </c>
       <c r="B322" t="n">
-        <v>1683.343417227615</v>
+        <v>1788.313411712947</v>
       </c>
       <c r="C322" t="n">
-        <v>1424.322543390032</v>
+        <v>1549.003971511687</v>
       </c>
       <c r="D322" t="n">
-        <v>1938.935274609969</v>
+        <v>2027.609233907653</v>
       </c>
       <c r="E322" t="n">
-        <v>1672.280639648438</v>
+        <v>1744.484619140625</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
-        <v>46185</v>
+        <v>46213</v>
       </c>
       <c r="B323" t="n">
-        <v>1671.538227555983</v>
+        <v>1804.881681885194</v>
       </c>
       <c r="C323" t="n">
-        <v>1418.500342764125</v>
+        <v>1569.161313603015</v>
       </c>
       <c r="D323" t="n">
-        <v>1942.523201336342</v>
+        <v>2033.187968789698</v>
       </c>
       <c r="E323" t="n">
-        <v>1665.127807617188</v>
+        <v>1795.693237304688</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
-        <v>46186</v>
+        <v>46214</v>
       </c>
       <c r="B324" t="n">
-        <v>1663.397639557702</v>
+        <v>1821.636248386377</v>
       </c>
       <c r="C324" t="n">
-        <v>1397.408393927848</v>
+        <v>1584.579620801047</v>
       </c>
       <c r="D324" t="n">
-        <v>1932.522193136389</v>
+        <v>2059.346981713737</v>
       </c>
       <c r="E324" t="n">
-        <v>1680.214599609375</v>
+        <v>1788.099609375</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
-        <v>46187</v>
+        <v>46215</v>
       </c>
       <c r="B325" t="n">
-        <v>1670.956480393407</v>
+        <v>1857.692891815382</v>
       </c>
       <c r="C325" t="n">
-        <v>1404.37635642593</v>
+        <v>1616.855969993959</v>
       </c>
       <c r="D325" t="n">
-        <v>1927.606715483877</v>
+        <v>2103.707339772605</v>
       </c>
       <c r="E325" t="n">
-        <v>1724.61328125</v>
+        <v>1805.7880859375</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
-        <v>46188</v>
+        <v>46216</v>
       </c>
       <c r="B326" t="n">
-        <v>1659.90743377863</v>
+        <v>1867.232872550656</v>
       </c>
       <c r="C326" t="n">
-        <v>1364.158725324003</v>
+        <v>1624.15874482069</v>
       </c>
       <c r="D326" t="n">
-        <v>1910.461462708739</v>
+        <v>2096.947735216805</v>
       </c>
       <c r="E326" t="n">
-        <v>1794.961181640625</v>
+        <v>1773.500732421875</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
-        <v>46189</v>
+        <v>46217</v>
       </c>
       <c r="B327" t="n">
-        <v>1641.048579415986</v>
+        <v>1870.705392070056</v>
       </c>
       <c r="C327" t="n">
-        <v>1375.421167780374</v>
+        <v>1640.097776973616</v>
       </c>
       <c r="D327" t="n">
-        <v>1890.892726861669</v>
+        <v>2114.805253449927</v>
       </c>
       <c r="E327" t="n">
-        <v>1790.398193359375</v>
+        <v>1889.479858398438</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
-        <v>46190</v>
+        <v>46218</v>
       </c>
       <c r="B328" t="n">
-        <v>1649.434961308777</v>
+        <v>1894.29870608573</v>
       </c>
       <c r="C328" t="n">
-        <v>1385.367878075126</v>
+        <v>1652.644658225181</v>
       </c>
       <c r="D328" t="n">
-        <v>1889.008837316741</v>
+        <v>2130.339086158983</v>
       </c>
       <c r="E328" t="n">
-        <v>1747.885498046875</v>
+        <v>1916.943725585938</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
-        <v>46191</v>
+        <v>46219</v>
       </c>
       <c r="B329" t="n">
-        <v>1599.06811977002</v>
+        <v>1863.874251232628</v>
       </c>
       <c r="C329" t="n">
-        <v>1315.395550379028</v>
+        <v>1603.35615193774</v>
       </c>
       <c r="D329" t="n">
-        <v>1862.337487423804</v>
+        <v>2104.409921092803</v>
       </c>
       <c r="E329" t="n">
-        <v>1709.533447265625</v>
+        <v>1863.193359375</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
-        <v>46192</v>
+        <v>46220</v>
       </c>
       <c r="B330" t="n">
-        <v>1598.999607610859</v>
+        <v>1869.677355904054</v>
       </c>
       <c r="C330" t="n">
-        <v>1333.216172191808</v>
+        <v>1638.229365641001</v>
       </c>
       <c r="D330" t="n">
-        <v>1860.656249452788</v>
+        <v>2099.429252466715</v>
       </c>
       <c r="E330" t="n">
-        <v>1710.982421875</v>
+        <v>1840.988159179688</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
-        <v>46193</v>
+        <v>46221</v>
       </c>
       <c r="B331" t="n">
-        <v>1603.480845741467</v>
+        <v>1875.076026082379</v>
       </c>
       <c r="C331" t="n">
-        <v>1336.658064279067</v>
+        <v>1642.974791313592</v>
       </c>
       <c r="D331" t="n">
-        <v>1884.021564562133</v>
+        <v>2099.61348916206</v>
       </c>
       <c r="E331" t="n">
-        <v>1739.301391601562</v>
+        <v>1861.39208984375</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
-        <v>46194</v>
+        <v>46222</v>
       </c>
       <c r="B332" t="n">
-        <v>1624.394122390255</v>
+        <v>1899.479229208188</v>
       </c>
       <c r="C332" t="n">
-        <v>1352.805290499781</v>
+        <v>1657.609659517965</v>
       </c>
       <c r="D332" t="n">
-        <v>1895.199135997215</v>
+        <v>2146.482232977585</v>
       </c>
       <c r="E332" t="n">
-        <v>1704.58056640625</v>
+        <v>1871.508544921875</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="B333" t="n">
-        <v>1627.252532705407</v>
+        <v>1897.371415446801</v>
       </c>
       <c r="C333" t="n">
-        <v>1377.760100460442</v>
+        <v>1672.29148877935</v>
       </c>
       <c r="D333" t="n">
-        <v>1888.786045491097</v>
+        <v>2125.995698306526</v>
       </c>
       <c r="E333" t="n">
-        <v>1726.510864257812</v>
+        <v>1903.758911132812</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="B334" t="n">
-        <v>1622.65113599714</v>
+        <v>1889.50732655762</v>
       </c>
       <c r="C334" t="n">
-        <v>1356.929524647823</v>
+        <v>1654.852981702629</v>
       </c>
       <c r="D334" t="n">
-        <v>1883.815662779204</v>
+        <v>2137.866718826569</v>
       </c>
       <c r="E334" t="n">
-        <v>1665.436767578125</v>
+        <v>1928.3837890625</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
-        <v>46197</v>
+        <v>46225</v>
       </c>
       <c r="B335" t="n">
-        <v>1645.42302899221</v>
+        <v>1902.375273672071</v>
       </c>
       <c r="C335" t="n">
-        <v>1400.808893685482</v>
+        <v>1658.854780900841</v>
       </c>
       <c r="D335" t="n">
-        <v>1908.013682973725</v>
+        <v>2143.847670325959</v>
       </c>
       <c r="E335" t="n">
-        <v>1619.924926757812</v>
+        <v>1933.490112304688</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
-        <v>46198</v>
+        <v>46226</v>
       </c>
       <c r="B336" t="n">
-        <v>1609.33416619115</v>
+        <v>1862.12346056463</v>
       </c>
       <c r="C336" t="n">
-        <v>1362.785913403914</v>
+        <v>1637.127752671053</v>
       </c>
       <c r="D336" t="n">
-        <v>1868.918231456522</v>
+        <v>2087.995754198035</v>
       </c>
       <c r="E336" t="n">
-        <v>1564.816650390625</v>
+        <v>1877.100219726562</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
-        <v>46199</v>
+        <v>46227</v>
       </c>
       <c r="B337" t="n">
-        <v>1623.19281655776</v>
+        <v>1859.263139592103</v>
       </c>
       <c r="C337" t="n">
-        <v>1347.897487211248</v>
+        <v>1602.393169566829</v>
       </c>
       <c r="D337" t="n">
-        <v>1895.140179680811</v>
+        <v>2095.062629863915</v>
       </c>
       <c r="E337" t="n">
-        <v>1576.616088867188</v>
+        <v>1860.1767578125</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
-        <v>46200</v>
+        <v>46228</v>
       </c>
       <c r="B338" t="n">
-        <v>1641.005856268973</v>
+        <v>1857.40030322171</v>
       </c>
       <c r="C338" t="n">
-        <v>1376.134963006532</v>
+        <v>1626.054526458625</v>
       </c>
       <c r="D338" t="n">
-        <v>1883.27696629914</v>
+        <v>2118.344614726696</v>
       </c>
       <c r="E338" t="n">
-        <v>1571.588256835938</v>
+        <v>1873.222412109375</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
-        <v>46201</v>
+        <v>46229</v>
       </c>
       <c r="B339" t="n">
-        <v>1674.41652605648</v>
+        <v>1876.147535589289</v>
       </c>
       <c r="C339" t="n">
-        <v>1418.929941973971</v>
+        <v>1649.490393532586</v>
       </c>
       <c r="D339" t="n">
-        <v>1946.732194745231</v>
+        <v>2120.06217684524</v>
       </c>
       <c r="E339" t="n">
-        <v>1570.361206054688</v>
+        <v>1953.411254882812</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
-        <v>46202</v>
+        <v>46230</v>
       </c>
       <c r="B340" t="n">
-        <v>1688.711258874284</v>
+        <v>1870.152948250399</v>
       </c>
       <c r="C340" t="n">
-        <v>1433.449093189062</v>
+        <v>1623.227285604202</v>
       </c>
       <c r="D340" t="n">
-        <v>1951.992294047405</v>
+        <v>2115.657635204463</v>
       </c>
       <c r="E340" t="n">
-        <v>1610.205810546875</v>
+        <v>1890.613525390625</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
-        <v>46203</v>
+        <v>46231</v>
       </c>
       <c r="B341" t="n">
-        <v>1694.277654138591</v>
+        <v>1860.290413075264</v>
       </c>
       <c r="C341" t="n">
-        <v>1414.161804297658</v>
+        <v>1615.565508369622</v>
       </c>
       <c r="D341" t="n">
-        <v>1965.506630705883</v>
+        <v>2106.651001387157</v>
       </c>
       <c r="E341" t="n">
-        <v>1569.583862304688</v>
+        <v>1919.948486328125</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
-        <v>46204</v>
+        <v>46232</v>
       </c>
       <c r="B342" t="n">
-        <v>1725.767091736298</v>
+        <v>1873.119409383149</v>
       </c>
       <c r="C342" t="n">
-        <v>1469.541100794389</v>
+        <v>1635.031001914477</v>
       </c>
       <c r="D342" t="n">
-        <v>1996.862982273022</v>
+        <v>2113.570534925435</v>
       </c>
       <c r="E342" t="n">
-        <v>1608.960693359375</v>
+        <v>1908.51904296875</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
-        <v>46205</v>
+        <v>46233</v>
       </c>
       <c r="B343" t="n">
-        <v>1696.795613623009</v>
+        <v>1834.809166614255</v>
       </c>
       <c r="C343" t="n">
-        <v>1445.074132736377</v>
+        <v>1596.827533121756</v>
       </c>
       <c r="D343" t="n">
-        <v>1948.550026086836</v>
+        <v>2061.306224652199</v>
       </c>
       <c r="E343" t="n">
-        <v>1698.16943359375</v>
+        <v>1917.372924804688</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
-        <v>46206</v>
+        <v>46234</v>
       </c>
       <c r="B344" t="n">
-        <v>1716.058767031261</v>
+        <v>1835.840960083901</v>
       </c>
       <c r="C344" t="n">
-        <v>1464.122443389448</v>
+        <v>1580.82342070991</v>
       </c>
       <c r="D344" t="n">
-        <v>1972.617471641835</v>
+        <v>2066.699027314915</v>
       </c>
       <c r="E344" t="n">
-        <v>1756.518676757812</v>
+        <v>1860.345947265625</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
-        <v>46207</v>
+        <v>46235</v>
       </c>
       <c r="B345" t="n">
-        <v>1737.492427916402</v>
+        <v>1839.740296476813</v>
       </c>
       <c r="C345" t="n">
-        <v>1470.921273925713</v>
+        <v>1617.566814210327</v>
       </c>
       <c r="D345" t="n">
-        <v>1993.739665167959</v>
+        <v>2078.025957572293</v>
       </c>
       <c r="E345" t="n">
-        <v>1779.032958984375</v>
+        <v>1843.417724609375</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
-        <v>46208</v>
+        <v>46236</v>
       </c>
       <c r="B346" t="n">
-        <v>1772.714071954506</v>
+        <v>1865.99060939509</v>
       </c>
       <c r="C346" t="n">
-        <v>1510.315852230075</v>
+        <v>1633.190618409959</v>
       </c>
       <c r="D346" t="n">
-        <v>2029.675333774577</v>
+        <v>2094.133051452447</v>
       </c>
       <c r="E346" t="n">
-        <v>1783.005981445312</v>
+        <v>1882.52197265625</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
-        <v>46209</v>
+        <v>46237</v>
       </c>
       <c r="B347" t="n">
-        <v>1787.031962774829</v>
+        <v>1869.06534697955</v>
       </c>
       <c r="C347" t="n">
-        <v>1525.082106973783</v>
+        <v>1616.540530356213</v>
       </c>
       <c r="D347" t="n">
-        <v>2050.872990451465</v>
+        <v>2121.54320872062</v>
       </c>
       <c r="E347" t="n">
-        <v>1797.57373046875</v>
+        <v>1858.256469726562</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
-        <v>46210</v>
+        <v>46238</v>
       </c>
       <c r="B348" t="n">
-        <v>1790.904227472061</v>
+        <v>1869.622585355933</v>
       </c>
       <c r="C348" t="n">
-        <v>1546.917348006148</v>
+        <v>1645.709067461135</v>
       </c>
       <c r="D348" t="n">
-        <v>2062.933727724946</v>
+        <v>2108.211264811042</v>
       </c>
       <c r="E348" t="n">
-        <v>1768.511474609375</v>
+        <v>1868.385864257812</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
-        <v>46211</v>
+        <v>46239</v>
       </c>
       <c r="B349" t="n">
-        <v>1819.10124011143</v>
+        <v>1893.970370785035</v>
       </c>
       <c r="C349" t="n">
-        <v>1559.096488719916</v>
+        <v>1649.437767812149</v>
       </c>
       <c r="D349" t="n">
-        <v>2085.05770473405</v>
+        <v>2137.295193376789</v>
       </c>
       <c r="E349" t="n">
-        <v>1742.677612304688</v>
+        <v>1906.526000976562</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
-        <v>46212</v>
+        <v>46240</v>
       </c>
       <c r="B350" t="n">
-        <v>1785.404905249201</v>
+        <v>1867.997325648939</v>
       </c>
       <c r="C350" t="n">
-        <v>1530.271919144638</v>
+        <v>1633.689711171557</v>
       </c>
       <c r="D350" t="n">
-        <v>2052.203191461256</v>
+        <v>2107.304612595045</v>
       </c>
       <c r="E350" t="n">
-        <v>1744.484619140625</v>
+        <v>1902.057495117188</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
-        <v>46213</v>
+        <v>46241</v>
       </c>
       <c r="B351" t="n">
-        <v>1798.720538329982</v>
+        <v>1881.882201713964</v>
       </c>
       <c r="C351" t="n">
-        <v>1533.950363461894</v>
+        <v>1626.730366961567</v>
       </c>
       <c r="D351" t="n">
-        <v>2061.841576792783</v>
+        <v>2112.547894448593</v>
       </c>
       <c r="E351" t="n">
-        <v>1795.693237304688</v>
+        <v>1913.279418945312</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
-        <v>46214</v>
+        <v>46242</v>
       </c>
       <c r="B352" t="n">
-        <v>1813.233403899773</v>
+        <v>1898.83392013324</v>
       </c>
       <c r="C352" t="n">
-        <v>1564.751646998013</v>
+        <v>1654.420511543346</v>
       </c>
       <c r="D352" t="n">
-        <v>2064.009978476919</v>
+        <v>2125.071012449599</v>
       </c>
       <c r="E352" t="n">
-        <v>1788.099609375</v>
+        <v>1915.532958984375</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
-        <v>46215</v>
+        <v>46243</v>
       </c>
       <c r="B353" t="n">
-        <v>1840.844460444083</v>
+        <v>1938.013503754757</v>
       </c>
       <c r="C353" t="n">
-        <v>1568.051950016189</v>
+        <v>1693.940327858828</v>
       </c>
       <c r="D353" t="n">
-        <v>2109.974834587883</v>
+        <v>2189.218164148353</v>
       </c>
       <c r="E353" t="n">
-        <v>1805.7880859375</v>
+        <v>1908.682739257812</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
-        <v>46216</v>
+        <v>46244</v>
       </c>
       <c r="B354" t="n">
-        <v>1847.172900757108</v>
+        <v>1953.574557529663</v>
       </c>
       <c r="C354" t="n">
-        <v>1567.879736362776</v>
+        <v>1711.295850777263</v>
       </c>
       <c r="D354" t="n">
-        <v>2094.25549447817</v>
+        <v>2189.424039528294</v>
       </c>
       <c r="E354" t="n">
-        <v>1773.500732421875</v>
+        <v>1871.278686523438</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
-        <v>46217</v>
+        <v>46245</v>
       </c>
       <c r="B355" t="n">
-        <v>1843.007612251839</v>
+        <v>1965.86619950776</v>
       </c>
       <c r="C355" t="n">
-        <v>1568.437734957219</v>
+        <v>1715.383777151702</v>
       </c>
       <c r="D355" t="n">
-        <v>2111.471962017107</v>
+        <v>2201.451192157807</v>
       </c>
       <c r="E355" t="n">
-        <v>1889.479858398438</v>
+        <v>1881.37353515625</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
-        <v>46218</v>
+        <v>46246</v>
       </c>
       <c r="B356" t="n">
-        <v>1863.461163765782</v>
+        <v>2000.906415607469</v>
       </c>
       <c r="C356" t="n">
-        <v>1604.580843143888</v>
+        <v>1759.184233856271</v>
       </c>
       <c r="D356" t="n">
-        <v>2112.888138099986</v>
+        <v>2233.537935095962</v>
       </c>
       <c r="E356" t="n">
-        <v>1916.943725585938</v>
+        <v>1878.135009765625</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
-        <v>46219</v>
+        <v>46247</v>
       </c>
       <c r="B357" t="n">
-        <v>1822.660123557207</v>
+        <v>1984.320151761427</v>
       </c>
       <c r="C357" t="n">
-        <v>1544.577598690402</v>
+        <v>1757.009944425835</v>
       </c>
       <c r="D357" t="n">
-        <v>2095.647874534468</v>
+        <v>2210.679229560327</v>
       </c>
       <c r="E357" t="n">
-        <v>1863.193359375</v>
+        <v>1883.991333007812</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
-        <v>46220</v>
+        <v>46248</v>
       </c>
       <c r="B358" t="n">
-        <v>1829.847639320042</v>
+        <v>2006.055619894401</v>
       </c>
       <c r="C358" t="n">
-        <v>1552.809310579429</v>
+        <v>1760.089557097043</v>
       </c>
       <c r="D358" t="n">
-        <v>2080.455924161909</v>
+        <v>2229.384115623931</v>
       </c>
       <c r="E358" t="n">
-        <v>1840.988159179688</v>
+        <v>1880.650024414062</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
-        <v>46221</v>
+        <v>46249</v>
       </c>
       <c r="B359" t="n">
-        <v>1839.530590190908</v>
+        <v>2029.130170733603</v>
       </c>
       <c r="C359" t="n">
-        <v>1569.246980418674</v>
+        <v>1787.485052051676</v>
       </c>
       <c r="D359" t="n">
-        <v>2100.220276164411</v>
+        <v>2268.10252616258</v>
       </c>
       <c r="E359" t="n">
-        <v>1861.39208984375</v>
+        <v>1880.908325195312</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
-        <v>46222</v>
+        <v>46250</v>
       </c>
       <c r="B360" t="n">
-        <v>1863.906116837806</v>
+        <v>2072.556978485266</v>
       </c>
       <c r="C360" t="n">
-        <v>1620.924547343294</v>
+        <v>1828.087673018487</v>
       </c>
       <c r="D360" t="n">
-        <v>2121.247344656173</v>
+        <v>2313.024757280031</v>
       </c>
       <c r="E360" t="n">
-        <v>1871.508544921875</v>
+        <v>1873.942993164062</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
-        <v>46223</v>
+        <v>46251</v>
       </c>
       <c r="B361" t="n">
-        <v>1868.8553769246</v>
+        <v>2090.389063234627</v>
       </c>
       <c r="C361" t="n">
-        <v>1603.937085729185</v>
+        <v>1848.573791207967</v>
       </c>
       <c r="D361" t="n">
-        <v>2129.406715558335</v>
+        <v>2332.350128264492</v>
       </c>
       <c r="E361" t="n">
-        <v>1903.758911132812</v>
+        <v>1912.2021484375</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
-        <v>46224</v>
+        <v>46252</v>
       </c>
       <c r="B362" t="n">
-        <v>1865.386902503855</v>
+        <v>2102.924458004497</v>
       </c>
       <c r="C362" t="n">
-        <v>1586.75890554712</v>
+        <v>1872.222235977517</v>
       </c>
       <c r="D362" t="n">
-        <v>2132.352982135878</v>
+        <v>2344.329815477015</v>
       </c>
       <c r="E362" t="n">
-        <v>1928.3837890625</v>
+        <v>1916.459594726562</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
-        <v>46225</v>
+        <v>46253</v>
       </c>
       <c r="B363" t="n">
-        <v>1888.783404534904</v>
+        <v>2136.180435292093</v>
       </c>
       <c r="C363" t="n">
-        <v>1627.345972141536</v>
+        <v>1904.658645921574</v>
       </c>
       <c r="D363" t="n">
-        <v>2164.475310751949</v>
+        <v>2379.264945695631</v>
       </c>
       <c r="E363" t="n">
-        <v>1933.490112304688</v>
+        <v>2251.4580078125</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
-        <v>46226</v>
+        <v>46254</v>
       </c>
       <c r="B364" t="n">
-        <v>1853.286047331782</v>
+        <v>2115.831087225727</v>
       </c>
       <c r="C364" t="n">
-        <v>1579.288465957577</v>
+        <v>1877.117929905479</v>
       </c>
       <c r="D364" t="n">
-        <v>2120.195287615697</v>
+        <v>2367.36250888313</v>
       </c>
       <c r="E364" t="n">
-        <v>1877.100219726562</v>
+        <v>2326.384765625</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
-        <v>46227</v>
+        <v>46255</v>
       </c>
       <c r="B365" t="n">
-        <v>1868.192314799075</v>
+        <v>2131.921755836213</v>
       </c>
       <c r="C365" t="n">
-        <v>1592.904119351111</v>
+        <v>1879.829450336751</v>
       </c>
       <c r="D365" t="n">
-        <v>2124.122749346641</v>
+        <v>2380.260720651227</v>
       </c>
       <c r="E365" t="n">
-        <v>1860.1767578125</v>
+        <v>2515.28173828125</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
-        <v>46228</v>
+        <v>46257</v>
       </c>
       <c r="B366" t="n">
-        <v>1887.999936488896</v>
+        <v>2182.096518277767</v>
       </c>
       <c r="C366" t="n">
-        <v>1646.016146221595</v>
+        <v>1949.594553782106</v>
       </c>
       <c r="D366" t="n">
-        <v>2154.056298388702</v>
+        <v>2425.372617165334</v>
       </c>
       <c r="E366" t="n">
-        <v>1873.222412109375</v>
+        <v>2379.10009765625</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
-        <v>46229</v>
+        <v>46258</v>
       </c>
       <c r="B367" t="n">
-        <v>1924.831799614568</v>
+        <v>2189.646450272876</v>
       </c>
       <c r="C367" t="n">
-        <v>1661.04005521418</v>
+        <v>1972.212610643777</v>
       </c>
       <c r="D367" t="n">
-        <v>2181.738990671337</v>
-      </c>
-      <c r="E367" t="n">
-        <v>1919.02001953125</v>
-      </c>
+        <v>2435.836531233154</v>
+      </c>
+      <c r="E367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
-        <v>46230</v>
+        <v>46259</v>
       </c>
       <c r="B368" t="n">
-        <v>1944.429772293975</v>
+        <v>2190.805414616738</v>
       </c>
       <c r="C368" t="n">
-        <v>1667.573261316462</v>
+        <v>1962.570484432816</v>
       </c>
       <c r="D368" t="n">
-        <v>2198.449588516951</v>
+        <v>2439.184756232971</v>
       </c>
       <c r="E368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
-        <v>46231</v>
+        <v>46260</v>
       </c>
       <c r="B369" t="n">
-        <v>1957.59984758606</v>
+        <v>2211.857995823787</v>
       </c>
       <c r="C369" t="n">
-        <v>1696.117619251838</v>
+        <v>1960.43761633954</v>
       </c>
       <c r="D369" t="n">
-        <v>2202.225024715015</v>
+        <v>2445.521008722101</v>
       </c>
       <c r="E369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
-        <v>46232</v>
+        <v>46261</v>
       </c>
       <c r="B370" t="n">
-        <v>1999.362439860281</v>
+        <v>2178.759415810833</v>
       </c>
       <c r="C370" t="n">
-        <v>1722.641044855695</v>
+        <v>1940.274901713233</v>
       </c>
       <c r="D370" t="n">
-        <v>2266.496038070445</v>
+        <v>2419.072290131861</v>
       </c>
       <c r="E370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
-        <v>46233</v>
+        <v>46262</v>
       </c>
       <c r="B371" t="n">
-        <v>1983.641795606998</v>
+        <v>2181.842030739805</v>
       </c>
       <c r="C371" t="n">
-        <v>1718.20459848668</v>
+        <v>1933.854584462897</v>
       </c>
       <c r="D371" t="n">
-        <v>2284.368236934937</v>
+        <v>2439.675173818763</v>
       </c>
       <c r="E371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
-        <v>46234</v>
+        <v>46263</v>
       </c>
       <c r="B372" t="n">
-        <v>2019.370533742905</v>
+        <v>2184.550020609842</v>
       </c>
       <c r="C372" t="n">
-        <v>1753.9010952475</v>
+        <v>1936.625626224124</v>
       </c>
       <c r="D372" t="n">
-        <v>2283.616728151224</v>
+        <v>2422.209466139647</v>
       </c>
       <c r="E372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
-        <v>46235</v>
+        <v>46264</v>
       </c>
       <c r="B373" t="n">
-        <v>2060.641632789829</v>
+        <v>2206.353844006606</v>
       </c>
       <c r="C373" t="n">
-        <v>1784.993675358294</v>
+        <v>1980.971007663232</v>
       </c>
       <c r="D373" t="n">
-        <v>2316.915221094015</v>
+        <v>2425.276442623421</v>
       </c>
       <c r="E373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
-        <v>46236</v>
+        <v>46265</v>
       </c>
       <c r="B374" t="n">
-        <v>2119.142600084449</v>
+        <v>2201.781340043743</v>
       </c>
       <c r="C374" t="n">
-        <v>1860.402398622185</v>
+        <v>1964.720252714085</v>
       </c>
       <c r="D374" t="n">
-        <v>2377.011815924365</v>
+        <v>2433.272888547772</v>
       </c>
       <c r="E374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
-        <v>46237</v>
+        <v>46266</v>
       </c>
       <c r="B375" t="n">
-        <v>2160.15952170231</v>
+        <v>2191.609658980592</v>
       </c>
       <c r="C375" t="n">
-        <v>1853.110588776668</v>
+        <v>1958.049451978342</v>
       </c>
       <c r="D375" t="n">
-        <v>2420.14387216798</v>
+        <v>2425.331944203798</v>
       </c>
       <c r="E375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
-        <v>46238</v>
+        <v>46267</v>
       </c>
       <c r="B376" t="n">
-        <v>2194.033146233043</v>
+        <v>2202.326318287162</v>
       </c>
       <c r="C376" t="n">
-        <v>1943.411147093889</v>
+        <v>1962.128482708884</v>
       </c>
       <c r="D376" t="n">
-        <v>2469.333915491738</v>
+        <v>2425.095294092279</v>
       </c>
       <c r="E376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
-        <v>46239</v>
+        <v>46268</v>
       </c>
       <c r="B377" t="n">
-        <v>2255.320554379975</v>
+        <v>2160.054056450438</v>
       </c>
       <c r="C377" t="n">
-        <v>1991.792054028376</v>
+        <v>1911.30660439663</v>
       </c>
       <c r="D377" t="n">
-        <v>2543.27452286266</v>
+        <v>2392.473163411029</v>
       </c>
       <c r="E377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
-        <v>46240</v>
+        <v>46269</v>
       </c>
       <c r="B378" t="n">
-        <v>2257.49608121019</v>
+        <v>2155.253344287182</v>
       </c>
       <c r="C378" t="n">
-        <v>1968.103183773955</v>
+        <v>1917.275204762002</v>
       </c>
       <c r="D378" t="n">
-        <v>2523.520962739557</v>
+        <v>2404.412802302798</v>
       </c>
       <c r="E378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
-        <v>46241</v>
+        <v>46270</v>
       </c>
       <c r="B379" t="n">
-        <v>2309.067203074092</v>
+        <v>2151.454303479056</v>
       </c>
       <c r="C379" t="n">
-        <v>2053.293728267</v>
+        <v>1891.094816206693</v>
       </c>
       <c r="D379" t="n">
-        <v>2575.539747881213</v>
+        <v>2390.423338303498</v>
       </c>
       <c r="E379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
-        <v>46242</v>
+        <v>46271</v>
       </c>
       <c r="B380" t="n">
-        <v>2363.737404061052</v>
+        <v>2168.169675882612</v>
       </c>
       <c r="C380" t="n">
-        <v>2111.039701949993</v>
+        <v>1915.429363633463</v>
       </c>
       <c r="D380" t="n">
-        <v>2630.873546319562</v>
+        <v>2403.722741666363</v>
       </c>
       <c r="E380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
-        <v>46243</v>
+        <v>46272</v>
       </c>
       <c r="B381" t="n">
-        <v>2432.850463517395</v>
+        <v>2159.925758160265</v>
       </c>
       <c r="C381" t="n">
-        <v>2174.058240395206</v>
+        <v>1936.257176877871</v>
       </c>
       <c r="D381" t="n">
-        <v>2691.464966194454</v>
+        <v>2391.410093685606</v>
       </c>
       <c r="E381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
-        <v>46244</v>
+        <v>46273</v>
       </c>
       <c r="B382" t="n">
-        <v>2481.403586759332</v>
+        <v>2147.455476174932</v>
       </c>
       <c r="C382" t="n">
-        <v>2230.108987936819</v>
+        <v>1897.521691150007</v>
       </c>
       <c r="D382" t="n">
-        <v>2759.93632085448</v>
+        <v>2383.816658389253</v>
       </c>
       <c r="E382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
-        <v>46245</v>
+        <v>46274</v>
       </c>
       <c r="B383" t="n">
-        <v>2519.511280468609</v>
+        <v>2157.161849594854</v>
       </c>
       <c r="C383" t="n">
-        <v>2250.506620091892</v>
+        <v>1907.141122460535</v>
       </c>
       <c r="D383" t="n">
-        <v>2791.069282361734</v>
+        <v>2414.815098338853</v>
       </c>
       <c r="E383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
-        <v>46246</v>
+        <v>46275</v>
       </c>
       <c r="B384" t="n">
-        <v>2581.573305196333</v>
+        <v>2115.046434835309</v>
       </c>
       <c r="C384" t="n">
-        <v>2305.034072103236</v>
+        <v>1862.441268532308</v>
       </c>
       <c r="D384" t="n">
-        <v>2840.209546042931</v>
+        <v>2351.585377782651</v>
       </c>
       <c r="E384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
-        <v>46247</v>
+        <v>46276</v>
       </c>
       <c r="B385" t="n">
-        <v>2580.980190734168</v>
+        <v>2111.416486664771</v>
       </c>
       <c r="C385" t="n">
-        <v>2320.239278410627</v>
+        <v>1858.206230610094</v>
       </c>
       <c r="D385" t="n">
-        <v>2843.141381262024</v>
+        <v>2347.907007683335</v>
       </c>
       <c r="E385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
-        <v>46248</v>
+        <v>46277</v>
       </c>
       <c r="B386" t="n">
-        <v>2626.231889159704</v>
+        <v>2109.622437120762</v>
       </c>
       <c r="C386" t="n">
-        <v>2358.735299067865</v>
+        <v>1879.467973197115</v>
       </c>
       <c r="D386" t="n">
-        <v>2882.392892392304</v>
+        <v>2365.902395658776</v>
       </c>
       <c r="E386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
-        <v>46249</v>
+        <v>46278</v>
       </c>
       <c r="B387" t="n">
-        <v>2671.101491251867</v>
+        <v>2128.977157176071</v>
       </c>
       <c r="C387" t="n">
-        <v>2405.067212285885</v>
+        <v>1880.162071775669</v>
       </c>
       <c r="D387" t="n">
-        <v>2917.177175958807</v>
+        <v>2371.377400027007</v>
       </c>
       <c r="E387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
-        <v>46250</v>
+        <v>46279</v>
       </c>
       <c r="B388" t="n">
-        <v>2727.078409578323</v>
+        <v>2123.79371595256</v>
       </c>
       <c r="C388" t="n">
-        <v>2472.165881216622</v>
+        <v>1885.539360062196</v>
       </c>
       <c r="D388" t="n">
-        <v>2993.07939473492</v>
+        <v>2370.936776470344</v>
       </c>
       <c r="E388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
-        <v>46251</v>
+        <v>46280</v>
       </c>
       <c r="B389" t="n">
-        <v>2759.378464598222</v>
+        <v>2114.585596613804</v>
       </c>
       <c r="C389" t="n">
-        <v>2485.723044938537</v>
+        <v>1879.78766733738</v>
       </c>
       <c r="D389" t="n">
-        <v>3019.116649922245</v>
+        <v>2358.422613099725</v>
       </c>
       <c r="E389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
-        <v>46252</v>
+        <v>46281</v>
       </c>
       <c r="B390" t="n">
-        <v>2778.402841967857</v>
+        <v>2127.537395052492</v>
       </c>
       <c r="C390" t="n">
-        <v>2513.339512052877</v>
+        <v>1882.448156140072</v>
       </c>
       <c r="D390" t="n">
-        <v>3041.606923889973</v>
+        <v>2362.998862666129</v>
       </c>
       <c r="E390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
-        <v>46253</v>
+        <v>46282</v>
       </c>
       <c r="B391" t="n">
-        <v>2818.899371243511</v>
+        <v>2088.440362982003</v>
       </c>
       <c r="C391" t="n">
-        <v>2540.47532090997</v>
+        <v>1840.503551014969</v>
       </c>
       <c r="D391" t="n">
-        <v>3074.083500950908</v>
+        <v>2325.612776960647</v>
       </c>
       <c r="E391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
-        <v>46254</v>
+        <v>46283</v>
       </c>
       <c r="B392" t="n">
-        <v>2794.659777728718</v>
+        <v>2087.406313967107</v>
       </c>
       <c r="C392" t="n">
-        <v>2524.982318901347</v>
+        <v>1839.251516884564</v>
       </c>
       <c r="D392" t="n">
-        <v>3051.774947445934</v>
+        <v>2305.397248909265</v>
       </c>
       <c r="E392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
-        <v>46255</v>
+        <v>46284</v>
       </c>
       <c r="B393" t="n">
-        <v>2814.628692256436</v>
+        <v>2087.611280756263</v>
       </c>
       <c r="C393" t="n">
-        <v>2537.949766473088</v>
+        <v>1859.752675717013</v>
       </c>
       <c r="D393" t="n">
-        <v>3071.144731960577</v>
+        <v>2346.795611163508</v>
       </c>
       <c r="E393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
-        <v>46256</v>
+        <v>46285</v>
       </c>
       <c r="B394" t="n">
-        <v>2833.056593109683</v>
+        <v>2108.22019702811</v>
       </c>
       <c r="C394" t="n">
-        <v>2572.364701199398</v>
+        <v>1852.959514801169</v>
       </c>
       <c r="D394" t="n">
-        <v>3109.450130219222</v>
+        <v>2332.706793553946</v>
       </c>
       <c r="E394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
-        <v>46257</v>
+        <v>46286</v>
       </c>
       <c r="B395" t="n">
-        <v>2861.931363811294</v>
+        <v>2103.429149903606</v>
       </c>
       <c r="C395" t="n">
-        <v>2596.514805160596</v>
+        <v>1852.431040512062</v>
       </c>
       <c r="D395" t="n">
-        <v>3126.485243524281</v>
+        <v>2339.556289840054</v>
       </c>
       <c r="E395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
-        <v>46258</v>
+        <v>46287</v>
       </c>
       <c r="B396" t="n">
-        <v>2866.976207956712</v>
+        <v>2093.66902300285</v>
       </c>
       <c r="C396" t="n">
-        <v>2590.744112090316</v>
+        <v>1854.458339863475</v>
       </c>
       <c r="D396" t="n">
-        <v>3110.674151898831</v>
+        <v>2318.822480411434</v>
       </c>
       <c r="E396" t="inlineStr"/>
-    </row>
-    <row r="397">
-      <c r="A397" s="1" t="n">
-        <v>46259</v>
-      </c>
-      <c r="B397" t="n">
-        <v>2859.096210240826</v>
-      </c>
-      <c r="C397" t="n">
-        <v>2608.707799328436</v>
-      </c>
-      <c r="D397" t="n">
-        <v>3105.489904570794</v>
-      </c>
-      <c r="E397" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
